--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -766,8 +766,7 @@
     <t>1549: source value from ORDER - ITEM ORDERED (#100-7)</t>
   </si>
   <si>
-    <t>CPRSOrder.CPRSOrder.ItemOrderedParentFileIEN
-CPRSOrder.CPRSOrder.ItemOrderedParentFileNumber</t>
+    <t>CPRSOrder.CPRSOrder.ItemOrderedParentFileIEN,CPRSOrder.CPRSOrder.ItemOrderedParentFileNumber</t>
   </si>
   <si>
     <t>MedicationRequest.subject</t>
@@ -806,9 +805,7 @@
     <t>1226: reference from ORDER - OBJECT OF ORDER (#100-.02)</t>
   </si>
   <si>
-    <t>CPRSOrder.OrderAction.ObjectOfOrderIEN
-CPRSOrder.OrderAction.ObjectOfOrderPatientIEN
-CPRSOrder.OrderAction.ParentFileNumber</t>
+    <t>CPRSOrder.OrderAction.ObjectOfOrderIEN,CPRSOrder.OrderAction.ObjectOfOrderPatientIEN,CPRSOrder.OrderAction.ParentFileNumber</t>
   </si>
   <si>
     <t>MedicationRequest.encounter</t>
@@ -889,10 +886,7 @@
     <t>1228: source value from ORDER - WHEN ENTERED (#100-4)</t>
   </si>
   <si>
-    <t>CPRSOrder.CPRSOrder.EnteredDateTime
-CPRSOrder.CPRSOrder.EnteredVistaDate
-CPRSOrder.OrderedItem.EnteredDateTime
-CPRSOrder.OrderedItem.EnteredVistaDate</t>
+    <t>CPRSOrder.CPRSOrder.EnteredDateTime,CPRSOrder.CPRSOrder.EnteredVistaDate,CPRSOrder.OrderedItem.EnteredDateTime,CPRSOrder.OrderedItem.EnteredVistaDate</t>
   </si>
   <si>
     <t>MedicationRequest.requester</t>
@@ -1476,11 +1470,7 @@
     <t>1234: source value from ORDER - START DATE (#100-21)</t>
   </si>
   <si>
-    <t>CPRSOrder.CPRSOrder.OrderStartDateTime
-CPRSOrder.CPRSOrder.OrderStartVistaDate
-CPRSOrder.OrderAction.OrderStartDateTime
-CPRSOrder.OrderedItem.OrderStartDateTime
-CPRSOrder.OrderedItem.OrderStartVistaDate</t>
+    <t>CPRSOrder.CPRSOrder.OrderStartDateTime,CPRSOrder.CPRSOrder.OrderStartVistaDate,CPRSOrder.OrderAction.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartVistaDate</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.timing.repeat.bounds[x]:boundsPeriod.end</t>
@@ -1513,10 +1503,7 @@
     <t>1235: source value from ORDER - STOP DATE (#100-22)</t>
   </si>
   <si>
-    <t>CPRSOrder.CPRSOrder.OrderStopDateTime
-CPRSOrder.CPRSOrder.OrderStopVistaDate
-CPRSOrder.OrderedItem.OrderStopDateTime
-CPRSOrder.OrderedItem.OrderStopVistaDate</t>
+    <t>CPRSOrder.CPRSOrder.OrderStopDateTime,CPRSOrder.CPRSOrder.OrderStopVistaDate,CPRSOrder.OrderedItem.OrderStopDateTime,CPRSOrder.OrderedItem.OrderStopVistaDate</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.timing.repeat.count</t>
@@ -2744,7 +2731,7 @@
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="50.60546875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="207.35546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -250,12 +256,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Prescription
@@ -785,6 +785,12 @@
     <t>The subject on a medication request is mandatory.  For the secondary use case where the actual subject is not provided, there still must be an anonymized subject specified.</t>
   </si>
   <si>
+    <t>1226: reference from ORDER - OBJECT OF ORDER (#100-.02)</t>
+  </si>
+  <si>
+    <t>CPRSOrder.OrderAction.ObjectOfOrderIEN,CPRSOrder.OrderAction.ObjectOfOrderPatientIEN,CPRSOrder.OrderAction.ParentFileNumber</t>
+  </si>
+  <si>
     <t>Request.subject</t>
   </si>
   <si>
@@ -802,12 +808,6 @@
     <t>PID-3-Patient ID List</t>
   </si>
   <si>
-    <t>1226: reference from ORDER - OBJECT OF ORDER (#100-.02)</t>
-  </si>
-  <si>
-    <t>CPRSOrder.OrderAction.ObjectOfOrderIEN,CPRSOrder.OrderAction.ObjectOfOrderPatientIEN,CPRSOrder.OrderAction.ParentFileNumber</t>
-  </si>
-  <si>
     <t>MedicationRequest.encounter</t>
   </si>
   <si>
@@ -868,6 +868,12 @@
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
   </si>
   <si>
+    <t>1228: source value from ORDER - WHEN ENTERED (#100-4)</t>
+  </si>
+  <si>
+    <t>CPRSOrder.CPRSOrder.EnteredDateTime,CPRSOrder.CPRSOrder.EnteredVistaDate,CPRSOrder.OrderedItem.EnteredDateTime,CPRSOrder.OrderedItem.EnteredVistaDate</t>
+  </si>
+  <si>
     <t>Request.authoredOn</t>
   </si>
   <si>
@@ -881,12 +887,6 @@
   </si>
   <si>
     <t>RXE-32-Original Order Date/Time / ORC-9-Date/Time of Transaction</t>
-  </si>
-  <si>
-    <t>1228: source value from ORDER - WHEN ENTERED (#100-4)</t>
-  </si>
-  <si>
-    <t>CPRSOrder.CPRSOrder.EnteredDateTime,CPRSOrder.CPRSOrder.EnteredVistaDate,CPRSOrder.OrderedItem.EnteredDateTime,CPRSOrder.OrderedItem.EnteredVistaDate</t>
   </si>
   <si>
     <t>MedicationRequest.requester</t>
@@ -902,13 +902,13 @@
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
   </si>
   <si>
+    <t>1227: reference from ORDER - CURRENT AGENT/PROVIDER (#100-1)</t>
+  </si>
+  <si>
     <t>Request.requester</t>
   </si>
   <si>
     <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>1227: reference from ORDER - CURRENT AGENT/PROVIDER (#100-1)</t>
   </si>
   <si>
     <t>MedicationRequest.performer</t>
@@ -1461,18 +1461,18 @@
 </t>
   </si>
   <si>
+    <t>1234: source value from ORDER - START DATE (#100-21)</t>
+  </si>
+  <si>
+    <t>CPRSOrder.CPRSOrder.OrderStartDateTime,CPRSOrder.CPRSOrder.OrderStartVistaDate,CPRSOrder.OrderAction.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartVistaDate</t>
+  </si>
+  <si>
     <t>./low</t>
   </si>
   <si>
     <t>DR.1</t>
   </si>
   <si>
-    <t>1234: source value from ORDER - START DATE (#100-21)</t>
-  </si>
-  <si>
-    <t>CPRSOrder.CPRSOrder.OrderStartDateTime,CPRSOrder.CPRSOrder.OrderStartVistaDate,CPRSOrder.OrderAction.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartVistaDate</t>
-  </si>
-  <si>
     <t>MedicationRequest.dosageInstruction.timing.repeat.bounds[x]:boundsPeriod.end</t>
   </si>
   <si>
@@ -1494,16 +1494,16 @@
     <t>Period.end</t>
   </si>
   <si>
+    <t>1235: source value from ORDER - STOP DATE (#100-22)</t>
+  </si>
+  <si>
+    <t>CPRSOrder.CPRSOrder.OrderStopDateTime,CPRSOrder.CPRSOrder.OrderStopVistaDate,CPRSOrder.OrderedItem.OrderStopDateTime,CPRSOrder.OrderedItem.OrderStopVistaDate</t>
+  </si>
+  <si>
     <t>./high</t>
   </si>
   <si>
     <t>DR.2</t>
-  </si>
-  <si>
-    <t>1235: source value from ORDER - STOP DATE (#100-22)</t>
-  </si>
-  <si>
-    <t>CPRSOrder.CPRSOrder.OrderStopDateTime,CPRSOrder.CPRSOrder.OrderStopVistaDate,CPRSOrder.OrderedItem.OrderStopDateTime,CPRSOrder.OrderedItem.OrderStopVistaDate</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.timing.repeat.count</t>
@@ -2319,13 +2319,13 @@
     <t>A link to a resource representing an earlier order related order or prescription.</t>
   </si>
   <si>
+    <t>1232: reference from ORDER - REPLACED ORDER (#100-9)</t>
+  </si>
+  <si>
     <t>Request.replaces</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=?RPLC or ?SUCC]/target[classCode=SBADM,moodCode=RQO]</t>
-  </si>
-  <si>
-    <t>1232: reference from ORDER - REPLACED ORDER (#100-9)</t>
   </si>
   <si>
     <t>MedicationRequest.detectedIssue</t>
@@ -2725,13 +2725,13 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="207.35546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="207.35546875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="128.41796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2967,19 +2967,19 @@
         <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>83</v>
@@ -3586,13 +3586,13 @@
         <v>83</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP7" t="s" s="2">
         <v>83</v>
@@ -3709,13 +3709,13 @@
         <v>83</v>
       </c>
       <c r="AM8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP8" t="s" s="2">
         <v>83</v>
@@ -3832,13 +3832,13 @@
         <v>83</v>
       </c>
       <c r="AM9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO9" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP9" t="s" s="2">
         <v>83</v>
@@ -3957,13 +3957,13 @@
         <v>83</v>
       </c>
       <c r="AM10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO10" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>83</v>
@@ -4074,25 +4074,25 @@
         <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -4197,22 +4197,22 @@
         <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>83</v>
@@ -4320,19 +4320,19 @@
         <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>83</v>
@@ -4443,22 +4443,22 @@
         <v>104</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>83</v>
@@ -4567,19 +4567,19 @@
         <v>83</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>83</v>
@@ -4692,19 +4692,19 @@
         <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>83</v>
@@ -4810,22 +4810,22 @@
         <v>104</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>83</v>
@@ -4939,13 +4939,13 @@
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -5060,13 +5060,13 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -5173,25 +5173,25 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -5296,25 +5296,25 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>237</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -5542,25 +5542,25 @@
         <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -5663,22 +5663,22 @@
         <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>83</v>
@@ -5911,13 +5911,13 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>281</v>
+        <v>83</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>83</v>
+        <v>247</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>282</v>
@@ -6026,22 +6026,22 @@
         <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>83</v>
@@ -6149,19 +6149,19 @@
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -6276,16 +6276,16 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>83</v>
@@ -6393,25 +6393,25 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -6516,22 +6516,22 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -6637,19 +6637,19 @@
         <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -6764,13 +6764,13 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -6879,19 +6879,19 @@
         <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
@@ -7002,19 +7002,19 @@
         <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
@@ -7131,13 +7131,13 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>83</v>
@@ -7246,19 +7246,19 @@
         <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AL37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -7367,19 +7367,19 @@
         <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
@@ -7490,19 +7490,19 @@
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -7617,13 +7617,13 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -7740,13 +7740,13 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7865,13 +7865,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7988,19 +7988,19 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AN43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -8111,19 +8111,19 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AN44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="45" hidden="true">
@@ -8236,19 +8236,19 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AN45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -8357,19 +8357,19 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AN46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -8482,13 +8482,13 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -8603,13 +8603,13 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -8726,13 +8726,13 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
@@ -8851,13 +8851,13 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8974,13 +8974,13 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -9097,13 +9097,13 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -9218,13 +9218,13 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -9341,13 +9341,13 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -9460,13 +9460,13 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9583,13 +9583,13 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9704,13 +9704,13 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9827,13 +9827,13 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -9944,22 +9944,22 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>83</v>
+        <v>460</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>83</v>
+        <v>461</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>460</v>
+        <v>83</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>462</v>
+        <v>83</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>463</v>
@@ -10069,22 +10069,22 @@
         <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>83</v>
+        <v>471</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>83</v>
+        <v>472</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>471</v>
+        <v>83</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>473</v>
+        <v>83</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>474</v>
@@ -10200,13 +10200,13 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
@@ -10321,13 +10321,13 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
@@ -10446,13 +10446,13 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>83</v>
@@ -10571,13 +10571,13 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10692,13 +10692,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10815,13 +10815,13 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO66" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10936,13 +10936,13 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -11057,13 +11057,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -11178,13 +11178,13 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -11299,13 +11299,13 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -11420,13 +11420,13 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -11543,13 +11543,13 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>83</v>
@@ -11668,13 +11668,13 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO73" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>83</v>
@@ -11789,13 +11789,13 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
@@ -11912,13 +11912,13 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -12035,19 +12035,19 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="AN76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO76" t="s" s="2">
+      <c r="AP76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="77" hidden="true">
@@ -12160,19 +12160,19 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO77" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="AN77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO77" t="s" s="2">
+      <c r="AP77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="78" hidden="true">
@@ -12283,19 +12283,19 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AN78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO78" t="s" s="2">
+      <c r="AP78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="79" hidden="true">
@@ -12408,19 +12408,19 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO79" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AN79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO79" t="s" s="2">
+      <c r="AP79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="80" hidden="true">
@@ -12535,13 +12535,13 @@
         <v>83</v>
       </c>
       <c r="AO80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ80" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ80" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="81" hidden="true">
@@ -12650,13 +12650,13 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>83</v>
@@ -12773,13 +12773,13 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12902,13 +12902,13 @@
         <v>83</v>
       </c>
       <c r="AO83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ83" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ83" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="84" hidden="true">
@@ -13021,19 +13021,19 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AN84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO84" t="s" s="2">
+      <c r="AP84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="85" hidden="true">
@@ -13146,19 +13146,19 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO85" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AN85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO85" t="s" s="2">
+      <c r="AP85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ85" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ85" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="86" hidden="true">
@@ -13271,19 +13271,19 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="AN86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO86" t="s" s="2">
+      <c r="AP86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ86" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ86" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="87" hidden="true">
@@ -13396,13 +13396,13 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO87" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
@@ -13519,13 +13519,13 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -13637,16 +13637,16 @@
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="AM89" t="s" s="2">
+      <c r="AO89" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -13761,13 +13761,13 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -13884,13 +13884,13 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
@@ -14009,13 +14009,13 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
@@ -14132,13 +14132,13 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
@@ -14253,13 +14253,13 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO94" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -14376,13 +14376,13 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO95" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
@@ -14501,13 +14501,13 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO96" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>83</v>
@@ -14622,13 +14622,13 @@
         <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>83</v>
@@ -14743,13 +14743,13 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>83</v>
@@ -14864,13 +14864,13 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>83</v>
@@ -14986,16 +14986,16 @@
         <v>83</v>
       </c>
       <c r="AL100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>687</v>
       </c>
-      <c r="AM100" t="s" s="2">
+      <c r="AO100" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
@@ -15109,22 +15109,22 @@
         <v>83</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="AN101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO101" t="s" s="2">
+      <c r="AP101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ101" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="102" hidden="true">
@@ -15230,22 +15230,22 @@
         <v>83</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="AM102" t="s" s="2">
+      <c r="AO102" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="AN102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO102" t="s" s="2">
+      <c r="AP102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="103" hidden="true">
@@ -15353,16 +15353,16 @@
         <v>83</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="AM103" t="s" s="2">
+      <c r="AO103" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>83</v>
@@ -15477,16 +15477,16 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO104" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="AN104" t="s" s="2">
+      <c r="AP104" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>83</v>
@@ -15595,16 +15595,16 @@
         <v>83</v>
       </c>
       <c r="AL105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="AM105" t="s" s="2">
+      <c r="AO105" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>83</v>
@@ -15719,13 +15719,13 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO106" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>83</v>
@@ -15842,13 +15842,13 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO107" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
@@ -15967,13 +15967,13 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO108" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>83</v>
@@ -16087,22 +16087,22 @@
         <v>83</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="AM109" t="s" s="2">
+      <c r="AO109" t="s" s="2">
         <v>727</v>
       </c>
-      <c r="AN109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO109" t="s" s="2">
+      <c r="AP109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ109" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ109" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="110" hidden="true">
@@ -16208,22 +16208,22 @@
         <v>83</v>
       </c>
       <c r="AL110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN110" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="AM110" t="s" s="2">
+      <c r="AO110" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="AN110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO110" t="s" s="2">
+      <c r="AP110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ110" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ110" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="111" hidden="true">
@@ -16329,19 +16329,19 @@
         <v>741</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>734</v>
+        <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>742</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>83</v>
+        <v>734</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>83</v>
+        <v>743</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>743</v>
+        <v>83</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>83</v>
@@ -16455,13 +16455,13 @@
         <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO112" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
@@ -16572,19 +16572,19 @@
         <v>104</v>
       </c>
       <c r="AK113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM113" t="s" s="2">
         <v>756</v>
       </c>
-      <c r="AL113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM113" t="s" s="2">
+      <c r="AN113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO113" t="s" s="2">
         <v>757</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4424" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4424" uniqueCount="759">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file ORDER (#100) to us-core-medicationrequest</t>
+    <t>This StructureDefinition contains the maps for VistA file ORDER (100) to us-core-medicationrequest</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -495,6 +495,9 @@
   </si>
   <si>
     <t>This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>1225: source value from ORDER - ORDER # (100-.01) case package like 'PS%' &amp; class 'I' &amp; [exclude supply]</t>
   </si>
   <si>
     <t>Request.identifier</t>
@@ -763,7 +766,7 @@
     <t>medicationCodeableConcept</t>
   </si>
   <si>
-    <t>1549: source value from ORDER - ITEM ORDERED (#100-7)</t>
+    <t>1549: source value from ORDER - ITEM ORDERED (100-7)</t>
   </si>
   <si>
     <t>CPRSOrder.CPRSOrder.ItemOrderedParentFileIEN,CPRSOrder.CPRSOrder.ItemOrderedParentFileNumber</t>
@@ -785,7 +788,7 @@
     <t>The subject on a medication request is mandatory.  For the secondary use case where the actual subject is not provided, there still must be an anonymized subject specified.</t>
   </si>
   <si>
-    <t>1226: reference from ORDER - OBJECT OF ORDER (#100-.02)</t>
+    <t>1226: reference from ORDER - OBJECT OF ORDER (100-.02)</t>
   </si>
   <si>
     <t>CPRSOrder.OrderAction.ObjectOfOrderIEN,CPRSOrder.OrderAction.ObjectOfOrderPatientIEN,CPRSOrder.OrderAction.ParentFileNumber</t>
@@ -868,7 +871,7 @@
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
   </si>
   <si>
-    <t>1228: source value from ORDER - WHEN ENTERED (#100-4)</t>
+    <t>1228: source value from ORDER - WHEN ENTERED (100-4)</t>
   </si>
   <si>
     <t>CPRSOrder.CPRSOrder.EnteredDateTime,CPRSOrder.CPRSOrder.EnteredVistaDate,CPRSOrder.OrderedItem.EnteredDateTime,CPRSOrder.OrderedItem.EnteredVistaDate</t>
@@ -902,7 +905,7 @@
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
   </si>
   <si>
-    <t>1227: reference from ORDER - CURRENT AGENT/PROVIDER (#100-1)</t>
+    <t>1227: reference from ORDER - CURRENT AGENT/PROVIDER (100-1)</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -1461,7 +1464,7 @@
 </t>
   </si>
   <si>
-    <t>1234: source value from ORDER - START DATE (#100-21)</t>
+    <t>1234: source value from ORDER - START DATE (100-21)</t>
   </si>
   <si>
     <t>CPRSOrder.CPRSOrder.OrderStartDateTime,CPRSOrder.CPRSOrder.OrderStartVistaDate,CPRSOrder.OrderAction.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartVistaDate</t>
@@ -1494,7 +1497,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>1235: source value from ORDER - STOP DATE (#100-22)</t>
+    <t>1235: source value from ORDER - STOP DATE (100-22)</t>
   </si>
   <si>
     <t>CPRSOrder.CPRSOrder.OrderStopDateTime,CPRSOrder.CPRSOrder.OrderStopVistaDate,CPRSOrder.OrderedItem.OrderStopDateTime,CPRSOrder.OrderedItem.OrderStopVistaDate</t>
@@ -2319,7 +2322,7 @@
     <t>A link to a resource representing an earlier order related order or prescription.</t>
   </si>
   <si>
-    <t>1232: reference from ORDER - REPLACED ORDER (#100-9)</t>
+    <t>1232: reference from ORDER - REPLACED ORDER (100-9)</t>
   </si>
   <si>
     <t>Request.replaces</t>
@@ -2725,7 +2728,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="99.9140625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="207.35546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
@@ -3991,7 +3994,7 @@
         <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>83</v>
@@ -4074,33 +4077,33 @@
         <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -4126,13 +4129,13 @@
         <v>112</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -4158,13 +4161,13 @@
         <v>83</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>83</v>
@@ -4182,7 +4185,7 @@
         <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>92</v>
@@ -4203,16 +4206,16 @@
         <v>83</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>83</v>
@@ -4220,10 +4223,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4246,16 +4249,16 @@
         <v>83</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4281,13 +4284,13 @@
         <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>83</v>
@@ -4305,7 +4308,7 @@
         <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -4326,13 +4329,13 @@
         <v>83</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>83</v>
@@ -4343,10 +4346,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4372,13 +4375,13 @@
         <v>112</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4404,13 +4407,13 @@
         <v>83</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>83</v>
@@ -4428,7 +4431,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>92</v>
@@ -4449,16 +4452,16 @@
         <v>83</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>83</v>
@@ -4466,10 +4469,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4492,16 +4495,16 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4527,29 +4530,29 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4573,13 +4576,13 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>83</v>
@@ -4587,13 +4590,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -4615,16 +4618,16 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4650,13 +4653,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4674,7 +4677,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4698,13 +4701,13 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>83</v>
@@ -4712,10 +4715,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4741,10 +4744,10 @@
         <v>112</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4771,13 +4774,13 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -4795,7 +4798,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4816,16 +4819,16 @@
         <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>83</v>
@@ -4833,10 +4836,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4859,16 +4862,16 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4918,7 +4921,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4945,7 +4948,7 @@
         <v>83</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4956,10 +4959,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4982,13 +4985,13 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -5039,7 +5042,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -5066,7 +5069,7 @@
         <v>83</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -5077,10 +5080,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5103,16 +5106,16 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -5138,27 +5141,27 @@
         <v>83</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>92</v>
@@ -5179,30 +5182,30 @@
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>83</v>
@@ -5224,16 +5227,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -5259,11 +5262,11 @@
         <v>83</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>83</v>
@@ -5281,7 +5284,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>92</v>
@@ -5296,33 +5299,33 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5345,16 +5348,16 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5404,7 +5407,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>92</v>
@@ -5419,33 +5422,33 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5468,16 +5471,16 @@
         <v>83</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5527,7 +5530,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5548,27 +5551,27 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5591,13 +5594,13 @@
         <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5648,7 +5651,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5669,16 +5672,16 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>83</v>
@@ -5686,10 +5689,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5712,13 +5715,13 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5769,7 +5772,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5784,33 +5787,33 @@
         <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5833,13 +5836,13 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5890,7 +5893,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5905,22 +5908,22 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>83</v>
@@ -5928,10 +5931,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5954,13 +5957,13 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6011,7 +6014,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -6032,16 +6035,16 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>83</v>
@@ -6049,10 +6052,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6075,16 +6078,16 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -6110,13 +6113,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -6134,7 +6137,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -6155,13 +6158,13 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -6172,10 +6175,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6198,13 +6201,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6255,7 +6258,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -6282,10 +6285,10 @@
         <v>83</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>83</v>
@@ -6293,10 +6296,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6319,16 +6322,16 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6354,13 +6357,13 @@
         <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>83</v>
@@ -6378,7 +6381,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6399,27 +6402,27 @@
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6442,16 +6445,16 @@
         <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6501,7 +6504,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6522,16 +6525,16 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -6539,10 +6542,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6565,13 +6568,13 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6622,7 +6625,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6643,13 +6646,13 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -6660,10 +6663,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6689,10 +6692,10 @@
         <v>106</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6743,7 +6746,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6770,7 +6773,7 @@
         <v>83</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -6781,10 +6784,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6807,13 +6810,13 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6864,7 +6867,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6885,13 +6888,13 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
@@ -6902,10 +6905,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6931,14 +6934,14 @@
         <v>150</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6987,7 +6990,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -7008,13 +7011,13 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
@@ -7025,10 +7028,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7051,16 +7054,16 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7086,13 +7089,13 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -7110,7 +7113,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -7137,7 +7140,7 @@
         <v>83</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>83</v>
@@ -7148,10 +7151,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7174,13 +7177,13 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7231,7 +7234,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -7252,13 +7255,13 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -7269,10 +7272,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7295,13 +7298,13 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7352,7 +7355,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7373,13 +7376,13 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
@@ -7390,10 +7393,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7416,16 +7419,16 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7475,7 +7478,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7496,13 +7499,13 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -7513,10 +7516,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7539,13 +7542,13 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7596,7 +7599,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7623,7 +7626,7 @@
         <v>83</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -7634,10 +7637,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7666,7 +7669,7 @@
         <v>139</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>141</v>
@@ -7707,19 +7710,19 @@
         <v>83</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7746,7 +7749,7 @@
         <v>83</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7757,14 +7760,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7786,10 +7789,10 @@
         <v>138</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>141</v>
@@ -7844,7 +7847,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7882,10 +7885,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7908,17 +7911,17 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7967,7 +7970,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7994,21 +7997,21 @@
         <v>83</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8031,17 +8034,17 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -8090,7 +8093,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -8117,21 +8120,21 @@
         <v>83</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8154,19 +8157,19 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -8191,13 +8194,13 @@
         <v>83</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>83</v>
@@ -8215,7 +8218,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -8242,21 +8245,21 @@
         <v>83</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8279,13 +8282,13 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8336,7 +8339,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8363,21 +8366,21 @@
         <v>83</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8400,19 +8403,19 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -8461,7 +8464,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8488,7 +8491,7 @@
         <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -8499,10 +8502,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8525,13 +8528,13 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8582,7 +8585,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8609,7 +8612,7 @@
         <v>83</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -8620,10 +8623,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8652,7 +8655,7 @@
         <v>139</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>141</v>
@@ -8693,19 +8696,19 @@
         <v>83</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8732,7 +8735,7 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
@@ -8743,14 +8746,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8772,10 +8775,10 @@
         <v>138</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>141</v>
@@ -8830,7 +8833,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8868,10 +8871,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8894,17 +8897,17 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8953,7 +8956,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8980,7 +8983,7 @@
         <v>83</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8991,10 +8994,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9017,17 +9020,17 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -9076,7 +9079,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -9088,7 +9091,7 @@
         <v>83</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>83</v>
@@ -9103,7 +9106,7 @@
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -9114,10 +9117,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9140,13 +9143,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9197,7 +9200,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -9224,7 +9227,7 @@
         <v>83</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -9235,10 +9238,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9267,7 +9270,7 @@
         <v>139</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>141</v>
@@ -9308,19 +9311,19 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9347,7 +9350,7 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -9358,10 +9361,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9384,13 +9387,13 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9429,17 +9432,17 @@
         <v>83</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9466,7 +9469,7 @@
         <v>83</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9477,13 +9480,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>83</v>
@@ -9505,13 +9508,13 @@
         <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9562,7 +9565,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9589,7 +9592,7 @@
         <v>83</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9600,10 +9603,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9626,13 +9629,13 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9683,7 +9686,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9710,7 +9713,7 @@
         <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9721,10 +9724,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9753,7 +9756,7 @@
         <v>139</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>141</v>
@@ -9794,19 +9797,19 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9833,7 +9836,7 @@
         <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -9844,10 +9847,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9870,16 +9873,16 @@
         <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9929,7 +9932,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9938,16 +9941,16 @@
         <v>92</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>83</v>
@@ -9956,21 +9959,21 @@
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9993,23 +9996,23 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q60" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="R60" t="s" s="2">
         <v>83</v>
@@ -10054,7 +10057,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -10063,16 +10066,16 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>83</v>
@@ -10081,21 +10084,21 @@
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10118,19 +10121,19 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10179,7 +10182,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10206,7 +10209,7 @@
         <v>83</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
@@ -10217,10 +10220,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10243,13 +10246,13 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10300,7 +10303,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10327,7 +10330,7 @@
         <v>83</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
@@ -10338,10 +10341,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10364,19 +10367,19 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10425,7 +10428,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10452,7 +10455,7 @@
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>83</v>
@@ -10463,10 +10466,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10489,19 +10492,19 @@
         <v>93</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10550,7 +10553,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10577,7 +10580,7 @@
         <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10588,10 +10591,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10617,10 +10620,10 @@
         <v>112</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10647,13 +10650,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -10671,7 +10674,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10698,7 +10701,7 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10709,10 +10712,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10735,13 +10738,13 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10749,7 +10752,7 @@
         <v>83</v>
       </c>
       <c r="Q66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="R66" t="s" s="2">
         <v>83</v>
@@ -10794,7 +10797,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10821,7 +10824,7 @@
         <v>83</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10832,10 +10835,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10858,13 +10861,13 @@
         <v>93</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10915,7 +10918,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10942,7 +10945,7 @@
         <v>83</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10953,10 +10956,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10979,13 +10982,13 @@
         <v>93</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -11036,7 +11039,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -11063,7 +11066,7 @@
         <v>83</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -11074,10 +11077,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11100,13 +11103,13 @@
         <v>93</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11157,7 +11160,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -11184,7 +11187,7 @@
         <v>83</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -11195,10 +11198,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11224,10 +11227,10 @@
         <v>112</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11254,13 +11257,13 @@
         <v>83</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -11278,7 +11281,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11305,7 +11308,7 @@
         <v>83</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -11316,10 +11319,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11345,13 +11348,13 @@
         <v>112</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11377,11 +11380,11 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -11399,7 +11402,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11426,7 +11429,7 @@
         <v>83</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -11437,10 +11440,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11463,16 +11466,16 @@
         <v>93</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11522,7 +11525,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11549,7 +11552,7 @@
         <v>83</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>83</v>
@@ -11560,10 +11563,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11589,16 +11592,16 @@
         <v>112</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11623,13 +11626,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -11647,7 +11650,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11674,7 +11677,7 @@
         <v>83</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>83</v>
@@ -11685,10 +11688,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11711,13 +11714,13 @@
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11768,7 +11771,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11795,7 +11798,7 @@
         <v>83</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
@@ -11806,10 +11809,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11832,16 +11835,16 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11870,10 +11873,10 @@
         <v>116</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11891,7 +11894,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11918,7 +11921,7 @@
         <v>83</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -11929,10 +11932,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11955,16 +11958,16 @@
         <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11990,13 +11993,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -12014,7 +12017,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -12041,21 +12044,21 @@
         <v>83</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12078,19 +12081,19 @@
         <v>93</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -12115,13 +12118,13 @@
         <v>83</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
@@ -12139,7 +12142,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -12166,21 +12169,21 @@
         <v>83</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12203,17 +12206,17 @@
         <v>93</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -12238,13 +12241,13 @@
         <v>83</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>83</v>
@@ -12262,7 +12265,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12289,21 +12292,21 @@
         <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12326,19 +12329,19 @@
         <v>93</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -12363,13 +12366,13 @@
         <v>83</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>83</v>
@@ -12387,7 +12390,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12414,21 +12417,21 @@
         <v>83</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12451,13 +12454,13 @@
         <v>93</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12508,7 +12511,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12541,15 +12544,15 @@
         <v>83</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12572,13 +12575,13 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12629,7 +12632,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12656,7 +12659,7 @@
         <v>83</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>83</v>
@@ -12667,10 +12670,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12699,7 +12702,7 @@
         <v>139</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>141</v>
@@ -12740,19 +12743,19 @@
         <v>83</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12779,7 +12782,7 @@
         <v>83</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12790,10 +12793,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12816,17 +12819,17 @@
         <v>93</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12851,13 +12854,13 @@
         <v>83</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>83</v>
@@ -12875,7 +12878,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12908,15 +12911,15 @@
         <v>83</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12939,19 +12942,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -13000,7 +13003,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13027,21 +13030,21 @@
         <v>83</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13064,19 +13067,19 @@
         <v>93</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -13125,7 +13128,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13152,21 +13155,21 @@
         <v>83</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13189,19 +13192,19 @@
         <v>93</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -13250,7 +13253,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13277,21 +13280,21 @@
         <v>83</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13314,19 +13317,19 @@
         <v>93</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -13375,7 +13378,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13402,7 +13405,7 @@
         <v>83</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
@@ -13413,10 +13416,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13439,17 +13442,17 @@
         <v>93</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -13498,7 +13501,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13525,7 +13528,7 @@
         <v>83</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -13536,10 +13539,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13562,13 +13565,13 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13619,7 +13622,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13643,10 +13646,10 @@
         <v>83</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -13657,10 +13660,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13683,13 +13686,13 @@
         <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13740,7 +13743,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13767,7 +13770,7 @@
         <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -13778,10 +13781,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13810,7 +13813,7 @@
         <v>139</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>141</v>
@@ -13863,7 +13866,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13890,7 +13893,7 @@
         <v>83</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
@@ -13901,14 +13904,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13930,10 +13933,10 @@
         <v>138</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>141</v>
@@ -13988,7 +13991,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -14026,10 +14029,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14052,16 +14055,16 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -14111,7 +14114,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14138,7 +14141,7 @@
         <v>83</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
@@ -14149,10 +14152,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14175,13 +14178,13 @@
         <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14232,7 +14235,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14259,7 +14262,7 @@
         <v>83</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -14270,10 +14273,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14302,7 +14305,7 @@
         <v>139</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>141</v>
@@ -14355,7 +14358,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14382,7 +14385,7 @@
         <v>83</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
@@ -14393,14 +14396,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -14422,10 +14425,10 @@
         <v>138</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>141</v>
@@ -14480,7 +14483,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14518,10 +14521,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14544,13 +14547,13 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14601,7 +14604,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14628,7 +14631,7 @@
         <v>83</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>83</v>
@@ -14639,10 +14642,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14665,13 +14668,13 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14722,7 +14725,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14749,7 +14752,7 @@
         <v>83</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>83</v>
@@ -14760,10 +14763,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14786,13 +14789,13 @@
         <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14843,7 +14846,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14870,7 +14873,7 @@
         <v>83</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>83</v>
@@ -14881,10 +14884,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14907,19 +14910,19 @@
         <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -14968,7 +14971,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14992,10 +14995,10 @@
         <v>83</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
@@ -15006,10 +15009,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15032,16 +15035,16 @@
         <v>83</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15091,7 +15094,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15115,24 +15118,24 @@
         <v>83</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15155,13 +15158,13 @@
         <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15212,7 +15215,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15236,24 +15239,24 @@
         <v>83</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15276,16 +15279,16 @@
         <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15335,7 +15338,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15359,10 +15362,10 @@
         <v>83</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>83</v>
@@ -15373,10 +15376,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15399,13 +15402,13 @@
         <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15456,7 +15459,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15483,10 +15486,10 @@
         <v>83</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>83</v>
@@ -15494,10 +15497,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15520,13 +15523,13 @@
         <v>83</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15577,7 +15580,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15601,10 +15604,10 @@
         <v>83</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>83</v>
@@ -15615,10 +15618,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15641,13 +15644,13 @@
         <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15698,7 +15701,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15725,7 +15728,7 @@
         <v>83</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>83</v>
@@ -15736,10 +15739,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15768,7 +15771,7 @@
         <v>139</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>141</v>
@@ -15821,7 +15824,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15848,7 +15851,7 @@
         <v>83</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
@@ -15859,14 +15862,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15888,10 +15891,10 @@
         <v>138</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>141</v>
@@ -15946,7 +15949,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15984,10 +15987,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16010,16 +16013,16 @@
         <v>83</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -16045,13 +16048,13 @@
         <v>83</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>83</v>
@@ -16069,7 +16072,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>92</v>
@@ -16093,24 +16096,24 @@
         <v>83</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16133,13 +16136,13 @@
         <v>83</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -16166,13 +16169,13 @@
         <v>83</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>83</v>
@@ -16190,7 +16193,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16214,24 +16217,24 @@
         <v>83</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16254,13 +16257,13 @@
         <v>83</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16311,7 +16314,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16326,19 +16329,19 @@
         <v>104</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
@@ -16349,14 +16352,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -16375,16 +16378,16 @@
         <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16434,7 +16437,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16461,7 +16464,7 @@
         <v>83</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
@@ -16472,10 +16475,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16498,16 +16501,16 @@
         <v>83</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16557,7 +16560,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16578,13 +16581,13 @@
         <v>83</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -791,7 +791,7 @@
     <t>1226: reference from ORDER - OBJECT OF ORDER (100-.02)</t>
   </si>
   <si>
-    <t>CPRSOrder.OrderAction.ObjectOfOrderIEN,CPRSOrder.OrderAction.ObjectOfOrderPatientIEN,CPRSOrder.OrderAction.ParentFileNumber</t>
+    <t>CPRSOrder.OrderAction.ObjectOfOrderIEN,CPRSOrder.OrderAction.ObjectofOrderLabReferralPatientIEN,CPRSOrder.OrderAction.ObjectOfOrderPatientIEN,CPRSOrder.OrderAction.ParentFileNumber,CPRSOrder.OrderedItem.PatientIEN</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -1467,7 +1467,7 @@
     <t>1234: source value from ORDER - START DATE (100-21)</t>
   </si>
   <si>
-    <t>CPRSOrder.CPRSOrder.OrderStartDateTime,CPRSOrder.CPRSOrder.OrderStartVistaDate,CPRSOrder.OrderAction.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartVistaDate</t>
+    <t>CPRSOrder.CPRSOrder.OrderStartDateTime,CPRSOrder.CPRSOrder.OrderStartVistaDate,CPRSOrder.OrderAction.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartDateSID,CPRSOrder.OrderedItem.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartVistaDate</t>
   </si>
   <si>
     <t>./low</t>
@@ -1500,7 +1500,7 @@
     <t>1235: source value from ORDER - STOP DATE (100-22)</t>
   </si>
   <si>
-    <t>CPRSOrder.CPRSOrder.OrderStopDateTime,CPRSOrder.CPRSOrder.OrderStopVistaDate,CPRSOrder.OrderedItem.OrderStopDateTime,CPRSOrder.OrderedItem.OrderStopVistaDate</t>
+    <t>CPRSOrder.CPRSOrder.OrderStopDateTime,CPRSOrder.CPRSOrder.OrderStopVistaDate,CPRSOrder.OrderedItem.OrderStopDateSID,CPRSOrder.OrderedItem.OrderStopDateTime,CPRSOrder.OrderedItem.OrderStopVistaDate</t>
   </si>
   <si>
     <t>./high</t>
@@ -2729,7 +2729,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="99.9140625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="207.35546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="248.09765625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -775,7 +775,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -895,7 +895,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson|Device)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -775,7 +775,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>
@@ -895,7 +895,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson|Device)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -775,7 +775,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -895,7 +895,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson|Device)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2742,7 +2742,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="99.9140625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="248.09765625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4537" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4537" uniqueCount="766">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -501,6 +501,9 @@
   </si>
   <si>
     <t>1225: source value from ORDER - ORDER # (100-.01) case package like 'PS%' &amp; class 'I' &amp; [exclude supply]</t>
+  </si>
+  <si>
+    <t>LabOrder.Order.Description,LabOrder.Priority.Description,RadOrder.Order.Description,RadOrder.ResultExtension.null,OtherOrder.OrderCategory.Description,OtherOrder.Order.Description,OtherOrder.VA.VAStatus.Description,OtherOrder.Priority.Description,OtherOrder.Order.OriginalText</t>
   </si>
   <si>
     <t>Request.identifier</t>
@@ -797,6 +800,9 @@
     <t>CPRSOrder.OrderAction.ObjectOfOrderIEN,CPRSOrder.OrderAction.ObjectofOrderLabReferralPatientIEN,CPRSOrder.OrderAction.ObjectOfOrderPatientIEN,CPRSOrder.OrderAction.ParentFileNumber,CPRSOrder.OrderedItem.PatientIEN</t>
   </si>
   <si>
+    <t>RadOrder.ResultExtension.null</t>
+  </si>
+  <si>
     <t>Request.subject</t>
   </si>
   <si>
@@ -880,7 +886,7 @@
     <t>CPRSOrder.CPRSOrder.EnteredDateTime,CPRSOrder.CPRSOrder.EnteredVistaDate,CPRSOrder.OrderedItem.EnteredDateTime,CPRSOrder.OrderedItem.EnteredVistaDate</t>
   </si>
   <si>
-    <t>order.entered</t>
+    <t>LabOrder.EnteredOn,LabOrder.CodeTable.SDACodingStandard,Medication.EnteredOn,RadOrder.EnteredOn,RadOrder.CodeTable.SDACodingStandard,RadOrder.ResultExtension.CaseNumber,OtherOrder.EnteredOn</t>
   </si>
   <si>
     <t>Request.authoredOn</t>
@@ -1476,7 +1482,7 @@
     <t>CPRSOrder.CPRSOrder.OrderStartDateTime,CPRSOrder.CPRSOrder.OrderStartVistaDate,CPRSOrder.OrderAction.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartDateSID,CPRSOrder.OrderedItem.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartVistaDate</t>
   </si>
   <si>
-    <t>order.start</t>
+    <t>LabOrder.FromTime,LabOrder.SpecimenCollectedTime,Medication.FromTime,RadOrder.FromTime,OtherOrder.FromTime</t>
   </si>
   <si>
     <t>./low</t>
@@ -1512,7 +1518,7 @@
     <t>CPRSOrder.CPRSOrder.OrderStopDateTime,CPRSOrder.CPRSOrder.OrderStopVistaDate,CPRSOrder.OrderedItem.OrderStopDateSID,CPRSOrder.OrderedItem.OrderStopDateTime,CPRSOrder.OrderedItem.OrderStopVistaDate</t>
   </si>
   <si>
-    <t>order.stop</t>
+    <t>LabOrder.ToTime,Medication.ToTime,RadOrder.ToTime,OtherOrder.ToTime</t>
   </si>
   <si>
     <t>./high</t>
@@ -2335,6 +2341,9 @@
   </si>
   <si>
     <t>1232: reference from ORDER - REPLACED ORDER (100-9)</t>
+  </si>
+  <si>
+    <t>LabOrder.LabOrderExtension.ReplacedOrder,Medication.MedicationExtension.ReplacedOrder,RadOrder.OrderExtension.ReplacedOrder,OtherOrder.OrderExtension.ReplacedOrder</t>
   </si>
   <si>
     <t>Request.replaces</t>
@@ -2742,7 +2751,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="99.9140625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="248.09765625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -4126,30 +4135,30 @@
         <v>84</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AR11" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -4175,13 +4184,13 @@
         <v>113</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -4207,13 +4216,13 @@
         <v>84</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>84</v>
@@ -4231,7 +4240,7 @@
         <v>84</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>93</v>
@@ -4255,16 +4264,16 @@
         <v>84</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AR12" t="s" s="2">
         <v>84</v>
@@ -4272,10 +4281,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4298,16 +4307,16 @@
         <v>84</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4333,13 +4342,13 @@
         <v>84</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>84</v>
@@ -4357,7 +4366,7 @@
         <v>84</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>82</v>
@@ -4381,13 +4390,13 @@
         <v>84</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -4398,10 +4407,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4427,13 +4436,13 @@
         <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4459,13 +4468,13 @@
         <v>84</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>84</v>
@@ -4483,7 +4492,7 @@
         <v>84</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>93</v>
@@ -4507,16 +4516,16 @@
         <v>84</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>84</v>
@@ -4524,10 +4533,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4550,16 +4559,16 @@
         <v>84</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4585,29 +4594,29 @@
         <v>84</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -4634,13 +4643,13 @@
         <v>84</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -4648,13 +4657,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>84</v>
@@ -4676,16 +4685,16 @@
         <v>84</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4711,13 +4720,13 @@
         <v>84</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>84</v>
@@ -4735,7 +4744,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4762,13 +4771,13 @@
         <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -4776,10 +4785,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4805,10 +4814,10 @@
         <v>113</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4835,13 +4844,13 @@
         <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>84</v>
@@ -4859,7 +4868,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4883,16 +4892,16 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>84</v>
@@ -4900,10 +4909,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4926,16 +4935,16 @@
         <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4985,7 +4994,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -5015,7 +5024,7 @@
         <v>84</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -5026,10 +5035,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5052,13 +5061,13 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -5109,7 +5118,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -5139,7 +5148,7 @@
         <v>84</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -5150,10 +5159,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5176,16 +5185,16 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -5211,27 +5220,27 @@
         <v>84</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>93</v>
@@ -5255,30 +5264,30 @@
         <v>84</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>84</v>
@@ -5300,16 +5309,16 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -5335,11 +5344,11 @@
         <v>84</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>84</v>
@@ -5357,7 +5366,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>93</v>
@@ -5372,36 +5381,36 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5424,16 +5433,16 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5483,7 +5492,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>93</v>
@@ -5498,36 +5507,36 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>84</v>
+        <v>248</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5550,16 +5559,16 @@
         <v>84</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5609,7 +5618,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5633,27 +5642,27 @@
         <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5676,13 +5685,13 @@
         <v>84</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5733,7 +5742,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5757,16 +5766,16 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5774,10 +5783,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5800,13 +5809,13 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5857,7 +5866,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5872,36 +5881,36 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5924,13 +5933,13 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5981,7 +5990,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5996,7 +6005,7 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>84</v>
@@ -6005,16 +6014,16 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>84</v>
@@ -6022,10 +6031,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6048,13 +6057,13 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6105,7 +6114,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6129,16 +6138,16 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -6146,10 +6155,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6172,16 +6181,16 @@
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -6207,13 +6216,13 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
@@ -6231,7 +6240,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6255,13 +6264,13 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -6272,10 +6281,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6298,13 +6307,13 @@
         <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6355,7 +6364,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6385,10 +6394,10 @@
         <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -6396,10 +6405,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6422,16 +6431,16 @@
         <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6457,13 +6466,13 @@
         <v>84</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>84</v>
@@ -6481,7 +6490,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6505,27 +6514,27 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6548,16 +6557,16 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6607,7 +6616,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6631,16 +6640,16 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6648,10 +6657,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6674,13 +6683,13 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6731,7 +6740,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6755,13 +6764,13 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6772,10 +6781,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6801,10 +6810,10 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6855,7 +6864,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6885,7 +6894,7 @@
         <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6896,10 +6905,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6922,13 +6931,13 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6979,7 +6988,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -7003,13 +7012,13 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -7020,10 +7029,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7049,14 +7058,14 @@
         <v>151</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -7105,7 +7114,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7129,13 +7138,13 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -7146,10 +7155,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7172,16 +7181,16 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7207,13 +7216,13 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -7231,7 +7240,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7261,7 +7270,7 @@
         <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -7272,10 +7281,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7298,13 +7307,13 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7355,7 +7364,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7379,13 +7388,13 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -7396,10 +7405,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7422,13 +7431,13 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7479,7 +7488,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7503,13 +7512,13 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7520,10 +7529,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7546,16 +7555,16 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7605,7 +7614,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7629,13 +7638,13 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7646,10 +7655,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7672,13 +7681,13 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7729,7 +7738,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7759,7 +7768,7 @@
         <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7770,10 +7779,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7802,7 +7811,7 @@
         <v>140</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>142</v>
@@ -7843,19 +7852,19 @@
         <v>84</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7885,7 +7894,7 @@
         <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7896,14 +7905,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7925,10 +7934,10 @@
         <v>139</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>142</v>
@@ -7983,7 +7992,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -8024,10 +8033,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8050,17 +8059,17 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -8109,7 +8118,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8139,21 +8148,21 @@
         <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8176,17 +8185,17 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8235,7 +8244,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8265,21 +8274,21 @@
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8302,19 +8311,19 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8339,13 +8348,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -8363,7 +8372,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8393,21 +8402,21 @@
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8430,13 +8439,13 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8487,7 +8496,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8517,21 +8526,21 @@
         <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8554,19 +8563,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8615,7 +8624,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8645,7 +8654,7 @@
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8656,10 +8665,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8682,13 +8691,13 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8739,7 +8748,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8769,7 +8778,7 @@
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8780,10 +8789,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8812,7 +8821,7 @@
         <v>140</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>142</v>
@@ -8853,19 +8862,19 @@
         <v>84</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8895,7 +8904,7 @@
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8906,14 +8915,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8935,10 +8944,10 @@
         <v>139</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>142</v>
@@ -8993,7 +9002,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9034,10 +9043,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9060,17 +9069,17 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -9119,7 +9128,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9149,7 +9158,7 @@
         <v>84</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -9160,10 +9169,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9186,17 +9195,17 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9245,7 +9254,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9257,7 +9266,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -9275,7 +9284,7 @@
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -9286,10 +9295,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9312,13 +9321,13 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9369,7 +9378,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9399,7 +9408,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9410,10 +9419,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9442,7 +9451,7 @@
         <v>140</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>142</v>
@@ -9483,19 +9492,19 @@
         <v>84</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9525,7 +9534,7 @@
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9536,10 +9545,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9562,13 +9571,13 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9607,17 +9616,17 @@
         <v>84</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9647,7 +9656,7 @@
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9658,13 +9667,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>84</v>
@@ -9686,13 +9695,13 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9743,7 +9752,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9773,7 +9782,7 @@
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9784,10 +9793,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9810,13 +9819,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9867,7 +9876,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9897,7 +9906,7 @@
         <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9908,10 +9917,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9940,7 +9949,7 @@
         <v>140</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>142</v>
@@ -9981,19 +9990,19 @@
         <v>84</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10023,7 +10032,7 @@
         <v>84</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -10034,10 +10043,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10060,16 +10069,16 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10119,7 +10128,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10128,19 +10137,19 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>84</v>
@@ -10149,21 +10158,21 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10186,23 +10195,23 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q60" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="R60" t="s" s="2">
         <v>84</v>
@@ -10247,7 +10256,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10256,19 +10265,19 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>84</v>
@@ -10277,21 +10286,21 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10314,19 +10323,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10375,7 +10384,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10405,7 +10414,7 @@
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10416,10 +10425,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10442,13 +10451,13 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10499,7 +10508,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10529,7 +10538,7 @@
         <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10540,10 +10549,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10566,19 +10575,19 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10627,7 +10636,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10657,7 +10666,7 @@
         <v>84</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10668,10 +10677,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10694,19 +10703,19 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10755,7 +10764,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10785,7 +10794,7 @@
         <v>84</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10796,10 +10805,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10825,10 +10834,10 @@
         <v>113</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10855,13 +10864,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10879,7 +10888,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10909,7 +10918,7 @@
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10920,10 +10929,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10946,13 +10955,13 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10960,7 +10969,7 @@
         <v>84</v>
       </c>
       <c r="Q66" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="R66" t="s" s="2">
         <v>84</v>
@@ -11005,7 +11014,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11035,7 +11044,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11046,10 +11055,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11072,13 +11081,13 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11129,7 +11138,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11159,7 +11168,7 @@
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -11170,10 +11179,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11196,13 +11205,13 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -11253,7 +11262,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11283,7 +11292,7 @@
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11294,10 +11303,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11320,13 +11329,13 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11377,7 +11386,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11407,7 +11416,7 @@
         <v>84</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11418,10 +11427,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11447,10 +11456,10 @@
         <v>113</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11477,13 +11486,13 @@
         <v>84</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11501,7 +11510,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11531,7 +11540,7 @@
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11542,10 +11551,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11571,13 +11580,13 @@
         <v>113</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11603,11 +11612,11 @@
         <v>84</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11625,7 +11634,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11655,7 +11664,7 @@
         <v>84</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11666,10 +11675,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11692,16 +11701,16 @@
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11751,7 +11760,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11781,7 +11790,7 @@
         <v>84</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11792,10 +11801,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11821,16 +11830,16 @@
         <v>113</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -11855,13 +11864,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -11879,7 +11888,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11909,7 +11918,7 @@
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11920,10 +11929,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11946,13 +11955,13 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -12003,7 +12012,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12033,7 +12042,7 @@
         <v>84</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12044,10 +12053,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12070,16 +12079,16 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12108,10 +12117,10 @@
         <v>117</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>84</v>
@@ -12129,7 +12138,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12159,7 +12168,7 @@
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -12170,10 +12179,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12196,16 +12205,16 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12231,13 +12240,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12255,7 +12264,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12285,21 +12294,21 @@
         <v>84</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12322,19 +12331,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12359,13 +12368,13 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -12383,7 +12392,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12413,21 +12422,21 @@
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12450,17 +12459,17 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12485,13 +12494,13 @@
         <v>84</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12509,7 +12518,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12539,21 +12548,21 @@
         <v>84</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12576,19 +12585,19 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12613,13 +12622,13 @@
         <v>84</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12637,7 +12646,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12667,21 +12676,21 @@
         <v>84</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12704,13 +12713,13 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12761,7 +12770,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12797,15 +12806,15 @@
         <v>84</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12828,13 +12837,13 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12885,7 +12894,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12915,7 +12924,7 @@
         <v>84</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -12926,10 +12935,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12958,7 +12967,7 @@
         <v>140</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>142</v>
@@ -12999,19 +13008,19 @@
         <v>84</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13041,7 +13050,7 @@
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13052,10 +13061,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13078,17 +13087,17 @@
         <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -13113,13 +13122,13 @@
         <v>84</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -13137,7 +13146,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13173,15 +13182,15 @@
         <v>84</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13204,19 +13213,19 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13265,7 +13274,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13295,21 +13304,21 @@
         <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13332,19 +13341,19 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13393,7 +13402,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13423,21 +13432,21 @@
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR85" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13460,19 +13469,19 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>84</v>
@@ -13521,7 +13530,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13551,21 +13560,21 @@
         <v>84</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR86" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13588,19 +13597,19 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
@@ -13649,7 +13658,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13679,7 +13688,7 @@
         <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13690,10 +13699,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13716,17 +13725,17 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13775,7 +13784,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13805,7 +13814,7 @@
         <v>84</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13816,10 +13825,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13842,13 +13851,13 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13899,7 +13908,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13926,10 +13935,10 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -13940,10 +13949,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13966,13 +13975,13 @@
         <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -14023,7 +14032,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14053,7 +14062,7 @@
         <v>84</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14064,10 +14073,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14096,7 +14105,7 @@
         <v>140</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>142</v>
@@ -14149,7 +14158,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14179,7 +14188,7 @@
         <v>84</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14190,14 +14199,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14219,10 +14228,10 @@
         <v>139</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>142</v>
@@ -14277,7 +14286,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14318,10 +14327,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14344,16 +14353,16 @@
         <v>84</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -14403,7 +14412,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14433,7 +14442,7 @@
         <v>84</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14444,10 +14453,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14470,13 +14479,13 @@
         <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14527,7 +14536,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14557,7 +14566,7 @@
         <v>84</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
@@ -14568,10 +14577,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14600,7 +14609,7 @@
         <v>140</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>142</v>
@@ -14653,7 +14662,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14683,7 +14692,7 @@
         <v>84</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
@@ -14694,14 +14703,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -14723,10 +14732,10 @@
         <v>139</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>142</v>
@@ -14781,7 +14790,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14822,10 +14831,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14848,13 +14857,13 @@
         <v>84</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14905,7 +14914,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -14935,7 +14944,7 @@
         <v>84</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -14946,10 +14955,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14972,13 +14981,13 @@
         <v>84</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -15029,7 +15038,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15059,7 +15068,7 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
@@ -15070,10 +15079,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15096,13 +15105,13 @@
         <v>84</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -15153,7 +15162,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15183,7 +15192,7 @@
         <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -15194,10 +15203,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15220,19 +15229,19 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
@@ -15281,7 +15290,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15308,10 +15317,10 @@
         <v>84</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15322,10 +15331,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15348,16 +15357,16 @@
         <v>84</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15407,7 +15416,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15434,24 +15443,24 @@
         <v>84</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15474,13 +15483,13 @@
         <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15531,7 +15540,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15558,24 +15567,24 @@
         <v>84</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR102" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15598,16 +15607,16 @@
         <v>84</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15657,7 +15666,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15684,10 +15693,10 @@
         <v>84</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
@@ -15698,10 +15707,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15724,13 +15733,13 @@
         <v>84</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15781,7 +15790,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15811,10 +15820,10 @@
         <v>84</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>84</v>
@@ -15822,10 +15831,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15848,13 +15857,13 @@
         <v>84</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15905,7 +15914,7 @@
         <v>84</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15932,10 +15941,10 @@
         <v>84</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>84</v>
@@ -15946,10 +15955,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15972,13 +15981,13 @@
         <v>84</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -16029,7 +16038,7 @@
         <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>82</v>
@@ -16059,7 +16068,7 @@
         <v>84</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>84</v>
@@ -16070,10 +16079,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16102,7 +16111,7 @@
         <v>140</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>142</v>
@@ -16155,7 +16164,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16185,7 +16194,7 @@
         <v>84</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>84</v>
@@ -16196,14 +16205,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -16225,10 +16234,10 @@
         <v>139</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>142</v>
@@ -16283,7 +16292,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16324,10 +16333,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16350,16 +16359,16 @@
         <v>84</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -16385,13 +16394,13 @@
         <v>84</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>84</v>
@@ -16409,7 +16418,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>93</v>
@@ -16436,24 +16445,24 @@
         <v>84</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16476,13 +16485,13 @@
         <v>84</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -16509,13 +16518,13 @@
         <v>84</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>84</v>
@@ -16533,7 +16542,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -16560,24 +16569,24 @@
         <v>84</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16600,13 +16609,13 @@
         <v>84</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16657,7 +16666,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16672,22 +16681,22 @@
         <v>105</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>84</v>
+        <v>749</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -16698,14 +16707,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -16724,16 +16733,16 @@
         <v>84</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16783,7 +16792,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -16813,7 +16822,7 @@
         <v>84</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -16824,10 +16833,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16850,16 +16859,16 @@
         <v>84</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16909,7 +16918,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -16933,13 +16942,13 @@
         <v>84</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -503,7 +503,7 @@
     <t>1225: source value from ORDER - ORDER # (100-.01) case package like 'PS%' &amp; class 'I' &amp; [exclude supply]</t>
   </si>
   <si>
-    <t>LabOrder.Order.Description,LabOrder.Priority.Description,RadOrder.Order.Description,RadOrder.ResultExtension.null,OtherOrder.OrderCategory.Description,OtherOrder.Order.Description,OtherOrder.VA.VAStatus.Description,OtherOrder.Priority.Description,OtherOrder.Order.OriginalText</t>
+    <t>RadOrder.OrderItem[Order].Description,RadOrder.Extension[ResultExtension].null,LabOrder.OrderItem[Order].Description,LabOrder.Priority.Description,OtherOrder.OrderCategory.Description,OtherOrder.OrderItem[Order].Description,OtherOrder.OrderStatus[VA.VAStatus].Description,OtherOrder.Priority.Description,OtherOrder.OrderItem[Order].OriginalText</t>
   </si>
   <si>
     <t>Request.identifier</t>
@@ -800,7 +800,7 @@
     <t>CPRSOrder.OrderAction.ObjectOfOrderIEN,CPRSOrder.OrderAction.ObjectofOrderLabReferralPatientIEN,CPRSOrder.OrderAction.ObjectOfOrderPatientIEN,CPRSOrder.OrderAction.ParentFileNumber,CPRSOrder.OrderedItem.PatientIEN</t>
   </si>
   <si>
-    <t>RadOrder.ResultExtension.null</t>
+    <t>RadOrder.Extension[ResultExtension].null</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -886,7 +886,7 @@
     <t>CPRSOrder.CPRSOrder.EnteredDateTime,CPRSOrder.CPRSOrder.EnteredVistaDate,CPRSOrder.OrderedItem.EnteredDateTime,CPRSOrder.OrderedItem.EnteredVistaDate</t>
   </si>
   <si>
-    <t>LabOrder.EnteredOn,LabOrder.CodeTable.SDACodingStandard,Medication.EnteredOn,RadOrder.EnteredOn,RadOrder.CodeTable.SDACodingStandard,RadOrder.ResultExtension.CaseNumber,OtherOrder.EnteredOn</t>
+    <t>RadOrder.EnteredOn,RadOrder.NationalItem[CodeTable].SDACodingStandard,RadOrder.Extension[ResultExtension].CaseNumber,LabOrder.EnteredOn,LabOrder.NationalItem[CodeTable].SDACodingStandard,OtherOrder.EnteredOn,Medication.EnteredOn</t>
   </si>
   <si>
     <t>Request.authoredOn</t>
@@ -1482,7 +1482,7 @@
     <t>CPRSOrder.CPRSOrder.OrderStartDateTime,CPRSOrder.CPRSOrder.OrderStartVistaDate,CPRSOrder.OrderAction.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartDateSID,CPRSOrder.OrderedItem.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartVistaDate</t>
   </si>
   <si>
-    <t>LabOrder.FromTime,LabOrder.SpecimenCollectedTime,Medication.FromTime,RadOrder.FromTime,OtherOrder.FromTime</t>
+    <t>RadOrder.FromTime,LabOrder.FromTime,LabOrder.SpecimenCollectedTime,OtherOrder.FromTime,Medication.FromTime</t>
   </si>
   <si>
     <t>./low</t>
@@ -1518,7 +1518,7 @@
     <t>CPRSOrder.CPRSOrder.OrderStopDateTime,CPRSOrder.CPRSOrder.OrderStopVistaDate,CPRSOrder.OrderedItem.OrderStopDateSID,CPRSOrder.OrderedItem.OrderStopDateTime,CPRSOrder.OrderedItem.OrderStopVistaDate</t>
   </si>
   <si>
-    <t>LabOrder.ToTime,Medication.ToTime,RadOrder.ToTime,OtherOrder.ToTime</t>
+    <t>RadOrder.ToTime,LabOrder.ToTime,OtherOrder.ToTime,Medication.ToTime</t>
   </si>
   <si>
     <t>./high</t>
@@ -2343,7 +2343,7 @@
     <t>1232: reference from ORDER - REPLACED ORDER (100-9)</t>
   </si>
   <si>
-    <t>LabOrder.LabOrderExtension.ReplacedOrder,Medication.MedicationExtension.ReplacedOrder,RadOrder.OrderExtension.ReplacedOrder,OtherOrder.OrderExtension.ReplacedOrder</t>
+    <t>RadOrder.Extension[OrderExtension].ReplacedOrder,LabOrder.Extension[LabOrderExtension].ReplacedOrder,OtherOrder.Extension[OrderExtension].ReplacedOrder,Medication.Extension[MedicationExtension].ReplacedOrder</t>
   </si>
   <si>
     <t>Request.replaces</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file ORDER (100) to us-core-medicationrequest</t>
+    <t>This StructureDefinition contains the maps for VistA file ORDER (100) to us-core-medicationrequest.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$116</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4537" uniqueCount="766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4657" uniqueCount="784">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -540,6 +540,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-status</t>
+  </si>
+  <si>
+    <t>2168: target not supported</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -607,6 +610,9 @@
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-intent</t>
   </si>
   <si>
+    <t>2169: target not supported</t>
+  </si>
+  <si>
     <t>Request.intent</t>
   </si>
   <si>
@@ -639,6 +645,9 @@
   </si>
   <si>
     <t>open</t>
+  </si>
+  <si>
+    <t>2170: target not supported</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -660,6 +669,9 @@
     <t>The type of medication order.</t>
   </si>
   <si>
+    <t>2171: target not supported</t>
+  </si>
+  <si>
     <t>MedicationRequest.priority</t>
   </si>
   <si>
@@ -716,7 +728,36 @@
     <t>Indicates if this record was captured as a secondary 'reported' record rather than as an original primary source-of-truth record.  It may also indicate the source of the report.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>.participation[typeCode=INF].role</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reported[x]:reportedBoolean</t>
+  </si>
+  <si>
+    <t>reportedBoolean</t>
+  </si>
+  <si>
+    <t>2172: target not supported</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reported[x]:reportedReference</t>
+  </si>
+  <si>
+    <t>reportedReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
+</t>
+  </si>
+  <si>
+    <t>2173: target not supported</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x]</t>
@@ -739,10 +780,6 @@
   </si>
   <si>
     <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -778,6 +815,19 @@
     <t>CPRSOrder.CPRSOrder.ItemOrderedParentFileIEN,CPRSOrder.CPRSOrder.ItemOrderedParentFileNumber</t>
   </si>
   <si>
+    <t>MedicationRequest.medication[x]:medicationReference</t>
+  </si>
+  <si>
+    <t>medicationReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-medication)
+</t>
+  </si>
+  <si>
+    <t>2174: target not supported</t>
+  </si>
+  <si>
     <t>MedicationRequest.subject</t>
   </si>
   <si>
@@ -836,6 +886,9 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter."    If there is a need to link to episodes of care they will be handled with an extension.</t>
   </si>
   <si>
+    <t>2175: target not supported</t>
+  </si>
+  <si>
     <t>Request.context</t>
   </si>
   <si>
@@ -1285,6 +1338,9 @@
   </si>
   <si>
     <t>Dosage.text</t>
+  </si>
+  <si>
+    <t>2176: target not supported</t>
   </si>
   <si>
     <t>RXO-6; RXE-21</t>
@@ -2711,7 +2767,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR113"/>
+  <dimension ref="A1:AR116"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="81.1875" customWidth="true" bestFit="true"/>
@@ -4255,7 +4311,7 @@
         <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>84</v>
@@ -4264,16 +4320,16 @@
         <v>84</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AR12" t="s" s="2">
         <v>84</v>
@@ -4281,10 +4337,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4307,16 +4363,16 @@
         <v>84</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4342,13 +4398,13 @@
         <v>84</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>84</v>
@@ -4366,7 +4422,7 @@
         <v>84</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>82</v>
@@ -4390,13 +4446,13 @@
         <v>84</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -4407,10 +4463,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4436,13 +4492,13 @@
         <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4471,10 +4527,10 @@
         <v>166</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>84</v>
@@ -4492,7 +4548,7 @@
         <v>84</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>93</v>
@@ -4507,7 +4563,7 @@
         <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>84</v>
@@ -4516,16 +4572,16 @@
         <v>84</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>84</v>
@@ -4533,10 +4589,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4559,16 +4615,16 @@
         <v>84</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4594,29 +4650,29 @@
         <v>84</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -4631,7 +4687,7 @@
         <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>84</v>
@@ -4643,13 +4699,13 @@
         <v>84</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -4657,13 +4713,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>84</v>
@@ -4685,16 +4741,16 @@
         <v>84</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4723,10 +4779,10 @@
         <v>166</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>84</v>
@@ -4744,7 +4800,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4759,7 +4815,7 @@
         <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>84</v>
@@ -4771,13 +4827,13 @@
         <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -4785,10 +4841,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4814,10 +4870,10 @@
         <v>113</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4847,28 +4903,28 @@
         <v>166</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Z17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4892,16 +4948,16 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>84</v>
@@ -4909,10 +4965,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4935,16 +4991,16 @@
         <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4994,7 +5050,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -5024,7 +5080,7 @@
         <v>84</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -5035,10 +5091,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5061,13 +5117,13 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -5106,19 +5162,17 @@
         <v>84</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -5148,7 +5202,7 @@
         <v>84</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -5159,18 +5213,20 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>93</v>
@@ -5185,17 +5241,15 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>228</v>
-      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -5220,30 +5274,34 @@
         <v>84</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>230</v>
+        <v>84</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AC20" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>93</v>
@@ -5255,7 +5313,7 @@
         <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>84</v>
+        <v>232</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>84</v>
@@ -5264,30 +5322,30 @@
         <v>84</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>232</v>
+        <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>233</v>
+        <v>84</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>235</v>
+        <v>84</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>236</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>84</v>
@@ -5309,17 +5367,15 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>228</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -5344,11 +5400,13 @@
         <v>84</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>230</v>
+        <v>84</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>84</v>
@@ -5366,10 +5424,10 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>93</v>
@@ -5381,36 +5439,36 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>240</v>
+        <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>232</v>
+        <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>233</v>
+        <v>84</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>235</v>
+        <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>236</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5433,16 +5491,16 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5468,31 +5526,27 @@
         <v>84</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>84</v>
+        <v>243</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>93</v>
@@ -5507,38 +5561,40 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AP22" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AR22" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AR22" t="s" s="2">
-        <v>253</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>84</v>
       </c>
@@ -5556,19 +5612,19 @@
         <v>84</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>255</v>
+        <v>175</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5594,13 +5650,11 @@
         <v>84</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>84</v>
+        <v>243</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
@@ -5618,10 +5672,10 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>93</v>
@@ -5633,38 +5687,40 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>251</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>84</v>
+        <v>252</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>170</v>
+        <v>245</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>262</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
       </c>
@@ -5673,27 +5729,29 @@
         <v>82</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5742,13 +5800,13 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>84</v>
@@ -5757,7 +5815,7 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>84</v>
+        <v>256</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>84</v>
@@ -5766,27 +5824,27 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>84</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5794,7 +5852,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>93</v>
@@ -5809,15 +5867,17 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5866,10 +5926,10 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>93</v>
@@ -5881,36 +5941,36 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5918,7 +5978,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>93</v>
@@ -5930,18 +5990,20 @@
         <v>84</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5990,7 +6052,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -6005,7 +6067,7 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>84</v>
@@ -6014,27 +6076,27 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>84</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6045,7 +6107,7 @@
         <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>84</v>
@@ -6057,13 +6119,13 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6114,13 +6176,13 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>84</v>
@@ -6138,16 +6200,16 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -6155,10 +6217,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6172,7 +6234,7 @@
         <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>84</v>
@@ -6181,17 +6243,15 @@
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>174</v>
+        <v>287</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -6216,13 +6276,13 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>299</v>
+        <v>84</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>300</v>
+        <v>84</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
@@ -6240,7 +6300,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6255,36 +6315,36 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>290</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>84</v>
+        <v>296</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>84</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6292,28 +6352,28 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6364,7 +6424,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6379,7 +6439,7 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>84</v>
+        <v>302</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
@@ -6388,16 +6448,16 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>307</v>
+        <v>267</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -6405,10 +6465,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6419,7 +6479,7 @@
         <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>84</v>
@@ -6431,17 +6491,15 @@
         <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>174</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -6466,13 +6524,13 @@
         <v>84</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>313</v>
+        <v>84</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>314</v>
+        <v>84</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>84</v>
@@ -6490,13 +6548,13 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>84</v>
@@ -6514,27 +6572,27 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>316</v>
+        <v>84</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>319</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6545,7 +6603,7 @@
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>84</v>
@@ -6554,19 +6612,19 @@
         <v>84</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>321</v>
+        <v>175</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6592,13 +6650,13 @@
         <v>84</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>84</v>
+        <v>316</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>84</v>
+        <v>317</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>84</v>
@@ -6616,13 +6674,13 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>84</v>
@@ -6640,16 +6698,16 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>318</v>
+        <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6657,10 +6715,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6671,7 +6729,7 @@
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>84</v>
@@ -6680,16 +6738,16 @@
         <v>84</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6740,13 +6798,13 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>84</v>
@@ -6764,16 +6822,16 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>331</v>
+        <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>84</v>
+        <v>325</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6781,10 +6839,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6804,18 +6862,20 @@
         <v>84</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>175</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6840,13 +6900,13 @@
         <v>84</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>84</v>
+        <v>330</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>84</v>
+        <v>331</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
@@ -6864,7 +6924,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6888,27 +6948,27 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>84</v>
+        <v>332</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>84</v>
+        <v>333</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>84</v>
+        <v>335</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>84</v>
+        <v>336</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6928,18 +6988,20 @@
         <v>84</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6988,7 +7050,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -7012,16 +7074,16 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>84</v>
+        <v>335</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -7029,10 +7091,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7043,7 +7105,7 @@
         <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>84</v>
@@ -7055,18 +7117,16 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>151</v>
+        <v>345</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>345</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
@@ -7114,13 +7174,13 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>84</v>
@@ -7138,13 +7198,13 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -7155,10 +7215,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7169,7 +7229,7 @@
         <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>84</v>
@@ -7178,20 +7238,18 @@
         <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -7216,13 +7274,13 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>352</v>
+        <v>84</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>353</v>
+        <v>84</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -7240,13 +7298,13 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>84</v>
@@ -7270,7 +7328,7 @@
         <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -7281,10 +7339,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7304,16 +7362,16 @@
         <v>84</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7364,7 +7422,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7388,13 +7446,13 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -7405,10 +7463,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7419,7 +7477,7 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>84</v>
@@ -7428,19 +7486,21 @@
         <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L38" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
@@ -7488,13 +7548,13 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>84</v>
@@ -7512,13 +7572,13 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>366</v>
+        <v>84</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7529,10 +7589,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7543,10 +7603,10 @@
         <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>84</v>
@@ -7555,16 +7615,16 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>369</v>
+        <v>175</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7590,13 +7650,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>84</v>
+        <v>370</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7614,13 +7674,13 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>84</v>
@@ -7638,13 +7698,13 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>373</v>
+        <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7655,10 +7715,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7669,7 +7729,7 @@
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>84</v>
@@ -7681,13 +7741,13 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7738,19 +7798,19 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7762,13 +7822,13 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7779,14 +7839,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7805,17 +7865,15 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>139</v>
+        <v>379</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>140</v>
+        <v>380</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7852,19 +7910,19 @@
         <v>84</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7876,7 +7934,7 @@
         <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>84</v>
@@ -7888,13 +7946,13 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>84</v>
+        <v>382</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>84</v>
+        <v>383</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7905,14 +7963,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7922,29 +7980,27 @@
         <v>83</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>139</v>
+        <v>386</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7992,7 +8048,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -8004,7 +8060,7 @@
         <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>84</v>
@@ -8016,13 +8072,13 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>136</v>
+        <v>391</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -8033,10 +8089,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8056,21 +8112,19 @@
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>395</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -8130,7 +8184,7 @@
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -8154,49 +8208,49 @@
         <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>398</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>376</v>
+        <v>139</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>400</v>
+        <v>140</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -8232,31 +8286,31 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -8280,19 +8334,19 @@
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>84</v>
+        <v>404</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -8305,25 +8359,25 @@
         <v>84</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="N45" t="s" s="2">
-        <v>408</v>
+        <v>142</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>409</v>
+        <v>148</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8348,13 +8402,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>410</v>
+        <v>84</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>411</v>
+        <v>84</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -8372,7 +8426,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8384,7 +8438,7 @@
         <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -8402,21 +8456,21 @@
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>397</v>
+        <v>136</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>413</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8439,16 +8493,18 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -8496,7 +8552,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8526,21 +8582,21 @@
         <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8554,7 +8610,7 @@
         <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>84</v>
@@ -8563,19 +8619,17 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8624,7 +8678,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8639,7 +8693,7 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>84</v>
+        <v>421</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>84</v>
@@ -8654,21 +8708,21 @@
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>84</v>
+        <v>422</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8679,7 +8733,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>84</v>
@@ -8688,19 +8742,23 @@
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>376</v>
+        <v>175</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>377</v>
+        <v>424</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8724,13 +8782,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>84</v>
+        <v>428</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>84</v>
+        <v>429</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8748,19 +8806,19 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>379</v>
+        <v>430</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>84</v>
@@ -8778,32 +8836,32 @@
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>84</v>
+        <v>431</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>84</v>
@@ -8812,20 +8870,18 @@
         <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>139</v>
+        <v>393</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>140</v>
+        <v>433</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8862,31 +8918,31 @@
         <v>84</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>385</v>
+        <v>435</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8904,56 +8960,56 @@
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>84</v>
+        <v>431</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>139</v>
+        <v>437</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>388</v>
+        <v>438</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>389</v>
+        <v>439</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>142</v>
+        <v>440</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>148</v>
+        <v>441</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -9002,19 +9058,19 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>390</v>
+        <v>442</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>84</v>
@@ -9032,7 +9088,7 @@
         <v>84</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>136</v>
+        <v>443</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -9043,10 +9099,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9057,7 +9113,7 @@
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
@@ -9066,21 +9122,19 @@
         <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>270</v>
+        <v>393</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>430</v>
+        <v>394</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>431</v>
+        <v>395</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>432</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -9128,19 +9182,19 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>433</v>
+        <v>396</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -9158,7 +9212,7 @@
         <v>84</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>434</v>
+        <v>397</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -9169,21 +9223,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
@@ -9192,21 +9246,21 @@
         <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>436</v>
+        <v>139</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>437</v>
+        <v>140</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>84</v>
       </c>
@@ -9242,31 +9296,31 @@
         <v>84</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>440</v>
+        <v>402</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>441</v>
+        <v>144</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -9284,7 +9338,7 @@
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>442</v>
+        <v>397</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -9295,42 +9349,46 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>84</v>
+        <v>404</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>376</v>
+        <v>139</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -9378,19 +9436,19 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -9408,7 +9466,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>380</v>
+        <v>136</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9419,14 +9477,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9442,21 +9500,21 @@
         <v>84</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>139</v>
+        <v>287</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>140</v>
+        <v>448</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -9492,19 +9550,19 @@
         <v>84</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>385</v>
+        <v>451</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9516,7 +9574,7 @@
         <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
@@ -9534,7 +9592,7 @@
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>380</v>
+        <v>452</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9545,10 +9603,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9571,16 +9629,18 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
@@ -9616,17 +9676,19 @@
         <v>84</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AC55" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9638,7 +9700,7 @@
         <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>459</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>84</v>
@@ -9656,7 +9718,7 @@
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9667,14 +9729,12 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>84</v>
       </c>
@@ -9692,16 +9752,16 @@
         <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>447</v>
+        <v>394</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>448</v>
+        <v>395</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9752,7 +9812,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>449</v>
+        <v>396</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9764,7 +9824,7 @@
         <v>84</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>84</v>
@@ -9782,7 +9842,7 @@
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>450</v>
+        <v>397</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9793,21 +9853,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
@@ -9819,15 +9879,17 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>376</v>
+        <v>139</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>377</v>
+        <v>140</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9864,31 +9926,31 @@
         <v>84</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>84</v>
@@ -9906,7 +9968,7 @@
         <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9917,21 +9979,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>84</v>
@@ -9940,20 +10002,18 @@
         <v>84</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>139</v>
+        <v>464</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>140</v>
+        <v>465</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9990,31 +10050,29 @@
         <v>84</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>385</v>
+        <v>467</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -10032,7 +10090,7 @@
         <v>84</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>380</v>
+        <v>468</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -10043,12 +10101,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>84</v>
       </c>
@@ -10060,7 +10120,7 @@
         <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>84</v>
@@ -10069,17 +10129,15 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>270</v>
+        <v>471</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10128,7 +10186,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10137,19 +10195,19 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>464</v>
+        <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>465</v>
+        <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>466</v>
+        <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>467</v>
+        <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>84</v>
@@ -10164,15 +10222,15 @@
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>469</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10186,33 +10244,29 @@
         <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>270</v>
+        <v>393</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>472</v>
+        <v>394</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q60" t="s" s="2">
-        <v>475</v>
-      </c>
+      <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
         <v>84</v>
       </c>
@@ -10256,7 +10310,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>476</v>
+        <v>396</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10265,19 +10319,19 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>464</v>
+        <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>477</v>
+        <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>478</v>
+        <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>479</v>
+        <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>84</v>
@@ -10286,32 +10340,32 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>480</v>
+        <v>397</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>481</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>84</v>
@@ -10320,23 +10374,21 @@
         <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>483</v>
+        <v>139</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>484</v>
+        <v>140</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>485</v>
+        <v>399</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -10372,31 +10424,31 @@
         <v>84</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>488</v>
+        <v>402</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>84</v>
@@ -10414,7 +10466,7 @@
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>489</v>
+        <v>397</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10425,10 +10477,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10442,7 +10494,7 @@
         <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>84</v>
@@ -10451,15 +10503,17 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>483</v>
+        <v>287</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10508,7 +10562,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10517,19 +10571,19 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>84</v>
+        <v>482</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>84</v>
+        <v>483</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>84</v>
+        <v>484</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>84</v>
+        <v>485</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>84</v>
@@ -10538,21 +10592,21 @@
         <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>84</v>
+        <v>487</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10566,7 +10620,7 @@
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>84</v>
@@ -10575,24 +10629,24 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>495</v>
+        <v>287</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q63" s="2"/>
+      <c r="Q63" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="R63" t="s" s="2">
         <v>84</v>
       </c>
@@ -10636,7 +10690,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10645,19 +10699,19 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>84</v>
+        <v>482</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>84</v>
+        <v>495</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>84</v>
+        <v>496</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>84</v>
+        <v>497</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>84</v>
@@ -10666,21 +10720,21 @@
         <v>84</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>84</v>
+        <v>499</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10703,19 +10757,19 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="N64" t="s" s="2">
-        <v>498</v>
-      </c>
       <c r="O64" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10764,7 +10818,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10794,7 +10848,7 @@
         <v>84</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10805,10 +10859,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10831,13 +10885,13 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>113</v>
+        <v>501</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10864,13 +10918,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>509</v>
+        <v>84</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>510</v>
+        <v>84</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10918,7 +10972,7 @@
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10929,10 +10983,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10955,7 +11009,7 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>483</v>
+        <v>513</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>514</v>
@@ -10963,14 +11017,16 @@
       <c r="M66" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+      <c r="N66" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q66" t="s" s="2">
-        <v>516</v>
-      </c>
+      <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
         <v>84</v>
       </c>
@@ -11014,7 +11070,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11044,7 +11100,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11055,10 +11111,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11081,16 +11137,20 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>483</v>
+        <v>513</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
       </c>
@@ -11138,7 +11198,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11168,7 +11228,7 @@
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -11179,10 +11239,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11205,13 +11265,13 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>495</v>
+        <v>113</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -11238,13 +11298,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>84</v>
+        <v>527</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -11262,7 +11322,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11292,7 +11352,7 @@
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>501</v>
+        <v>530</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11303,10 +11363,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11329,20 +11389,22 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q69" s="2"/>
+      <c r="Q69" t="s" s="2">
+        <v>534</v>
+      </c>
       <c r="R69" t="s" s="2">
         <v>84</v>
       </c>
@@ -11386,7 +11448,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11416,7 +11478,7 @@
         <v>84</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11427,10 +11489,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11453,13 +11515,13 @@
         <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>113</v>
+        <v>501</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>507</v>
+        <v>537</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11486,13 +11548,13 @@
         <v>84</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>509</v>
+        <v>84</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>510</v>
+        <v>84</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11510,7 +11572,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11540,7 +11602,7 @@
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11551,10 +11613,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11565,7 +11627,7 @@
         <v>82</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>84</v>
@@ -11577,17 +11639,15 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>113</v>
+        <v>513</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11612,11 +11672,13 @@
         <v>84</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="Y71" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z71" t="s" s="2">
-        <v>536</v>
+        <v>84</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11634,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>84</v>
@@ -11664,7 +11726,7 @@
         <v>84</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>380</v>
+        <v>519</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11675,10 +11737,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11689,7 +11751,7 @@
         <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>84</v>
@@ -11701,17 +11763,15 @@
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>539</v>
+        <v>513</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>542</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11760,13 +11820,13 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>84</v>
@@ -11790,7 +11850,7 @@
         <v>84</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>380</v>
+        <v>519</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11801,10 +11861,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11815,7 +11875,7 @@
         <v>82</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>84</v>
@@ -11830,17 +11890,13 @@
         <v>113</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O73" t="s" s="2">
         <v>548</v>
       </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>84</v>
       </c>
@@ -11867,34 +11923,34 @@
         <v>166</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>551</v>
-      </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>84</v>
@@ -11918,7 +11974,7 @@
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11929,10 +11985,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11943,7 +11999,7 @@
         <v>82</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>84</v>
@@ -11955,15 +12011,17 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>554</v>
+        <v>113</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -11988,13 +12046,11 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>84</v>
+        <v>554</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -12012,13 +12068,13 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>84</v>
@@ -12042,7 +12098,7 @@
         <v>84</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>558</v>
+        <v>397</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12053,10 +12109,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12067,7 +12123,7 @@
         <v>82</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>84</v>
@@ -12079,16 +12135,16 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>174</v>
+        <v>557</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12114,13 +12170,13 @@
         <v>84</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>563</v>
+        <v>84</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>564</v>
+        <v>84</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>84</v>
@@ -12138,13 +12194,13 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>84</v>
@@ -12168,7 +12224,7 @@
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>566</v>
+        <v>397</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -12179,10 +12235,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12193,7 +12249,7 @@
         <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>84</v>
@@ -12205,18 +12261,20 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>568</v>
+        <v>113</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
       </c>
@@ -12240,13 +12298,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12264,13 +12322,13 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>84</v>
@@ -12294,21 +12352,21 @@
         <v>84</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>576</v>
+        <v>84</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12331,20 +12389,16 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>174</v>
+        <v>572</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>581</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>84</v>
       </c>
@@ -12368,13 +12422,13 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>582</v>
+        <v>84</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>583</v>
+        <v>84</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -12392,7 +12446,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12422,21 +12476,21 @@
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>586</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12459,18 +12513,18 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>590</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>84</v>
       </c>
@@ -12494,13 +12548,13 @@
         <v>84</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12518,7 +12572,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12548,21 +12602,21 @@
         <v>84</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>595</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12585,20 +12639,18 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>174</v>
+        <v>586</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>600</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>84</v>
       </c>
@@ -12622,13 +12674,13 @@
         <v>84</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12646,7 +12698,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12676,21 +12728,21 @@
         <v>84</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>605</v>
+        <v>594</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12701,7 +12753,7 @@
         <v>82</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>84</v>
@@ -12713,16 +12765,20 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>436</v>
+        <v>175</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>599</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
       </c>
@@ -12746,13 +12802,13 @@
         <v>84</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>84</v>
+        <v>600</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>84</v>
+        <v>601</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>84</v>
@@ -12770,13 +12826,13 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>84</v>
@@ -12800,21 +12856,21 @@
         <v>84</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>84</v>
+        <v>603</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>610</v>
+        <v>604</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12834,19 +12890,21 @@
         <v>84</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>376</v>
+        <v>175</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>377</v>
+        <v>606</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>378</v>
+        <v>607</v>
       </c>
       <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>608</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>84</v>
       </c>
@@ -12870,13 +12928,13 @@
         <v>84</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>84</v>
+        <v>609</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>84</v>
+        <v>610</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -12894,7 +12952,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>379</v>
+        <v>611</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12906,7 +12964,7 @@
         <v>84</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>84</v>
@@ -12924,32 +12982,32 @@
         <v>84</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>380</v>
+        <v>612</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR81" t="s" s="2">
-        <v>84</v>
+        <v>613</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>84</v>
@@ -12958,21 +13016,23 @@
         <v>84</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>140</v>
+        <v>615</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>382</v>
+        <v>616</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>617</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>618</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
       </c>
@@ -12996,43 +13056,43 @@
         <v>84</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>84</v>
+        <v>619</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>84</v>
+        <v>620</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>385</v>
+        <v>621</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>84</v>
@@ -13050,21 +13110,21 @@
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>380</v>
+        <v>622</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>84</v>
+        <v>623</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13075,7 +13135,7 @@
         <v>82</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>84</v>
@@ -13087,18 +13147,16 @@
         <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>174</v>
+        <v>454</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="N83" s="2"/>
-      <c r="O83" t="s" s="2">
-        <v>616</v>
-      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>84</v>
       </c>
@@ -13122,13 +13180,13 @@
         <v>84</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>617</v>
+        <v>84</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>618</v>
+        <v>84</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -13146,13 +13204,13 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>84</v>
@@ -13182,15 +13240,15 @@
         <v>84</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13210,23 +13268,19 @@
         <v>84</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>622</v>
+        <v>393</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>626</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>84</v>
       </c>
@@ -13274,7 +13328,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>627</v>
+        <v>396</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13286,7 +13340,7 @@
         <v>84</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>84</v>
@@ -13304,32 +13358,32 @@
         <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>604</v>
+        <v>397</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>628</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>84</v>
@@ -13338,23 +13392,21 @@
         <v>84</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>630</v>
+        <v>139</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>631</v>
+        <v>140</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>632</v>
+        <v>399</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>634</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>84</v>
       </c>
@@ -13390,31 +13442,31 @@
         <v>84</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>635</v>
+        <v>402</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>84</v>
@@ -13432,21 +13484,21 @@
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>636</v>
+        <v>397</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR85" t="s" s="2">
-        <v>637</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13469,19 +13521,17 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>639</v>
+        <v>175</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>642</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>84</v>
@@ -13506,13 +13556,13 @@
         <v>84</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>84</v>
+        <v>635</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>84</v>
+        <v>636</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>84</v>
@@ -13530,7 +13580,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13560,21 +13610,21 @@
         <v>84</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>645</v>
+        <v>84</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR86" t="s" s="2">
-        <v>646</v>
+        <v>638</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13597,19 +13647,19 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
@@ -13658,7 +13708,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13688,21 +13738,21 @@
         <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>654</v>
+        <v>622</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>84</v>
+        <v>646</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13728,14 +13778,16 @@
         <v>648</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>651</v>
+      </c>
       <c r="O88" t="s" s="2">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13784,7 +13836,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13820,15 +13872,15 @@
         <v>84</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>84</v>
+        <v>655</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13848,19 +13900,23 @@
         <v>84</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="O89" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="L89" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>84</v>
       </c>
@@ -13908,7 +13964,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13935,24 +13991,24 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AQ89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR89" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AQ89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR89" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13972,19 +14028,23 @@
         <v>84</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>376</v>
+        <v>666</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>377</v>
+        <v>667</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>668</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>670</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
       </c>
@@ -14032,7 +14092,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>379</v>
+        <v>671</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14044,7 +14104,7 @@
         <v>84</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>84</v>
@@ -14062,7 +14122,7 @@
         <v>84</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>380</v>
+        <v>672</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14073,21 +14133,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>84</v>
@@ -14096,21 +14156,21 @@
         <v>84</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>139</v>
+        <v>666</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>140</v>
+        <v>674</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>675</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>676</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
       </c>
@@ -14158,19 +14218,19 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>385</v>
+        <v>677</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>84</v>
@@ -14188,7 +14248,7 @@
         <v>84</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>380</v>
+        <v>672</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14199,46 +14259,42 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>139</v>
+        <v>679</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>388</v>
+        <v>680</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>681</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>84</v>
       </c>
@@ -14286,19 +14342,19 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>390</v>
+        <v>678</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>84</v>
@@ -14313,10 +14369,10 @@
         <v>84</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>84</v>
+        <v>682</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>136</v>
+        <v>683</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14327,10 +14383,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>669</v>
+        <v>684</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>669</v>
+        <v>684</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14353,17 +14409,15 @@
         <v>84</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>661</v>
+        <v>393</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>670</v>
+        <v>394</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>672</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14412,7 +14466,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>669</v>
+        <v>396</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14424,7 +14478,7 @@
         <v>84</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>84</v>
@@ -14442,7 +14496,7 @@
         <v>84</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>673</v>
+        <v>397</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14453,21 +14507,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>84</v>
@@ -14479,15 +14533,17 @@
         <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>376</v>
+        <v>139</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>377</v>
+        <v>140</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14536,19 +14592,19 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>84</v>
@@ -14566,7 +14622,7 @@
         <v>84</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
@@ -14577,14 +14633,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>138</v>
+        <v>404</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -14597,24 +14653,26 @@
         <v>84</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>140</v>
+        <v>405</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
       </c>
@@ -14662,7 +14720,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14692,7 +14750,7 @@
         <v>84</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>380</v>
+        <v>136</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
@@ -14703,46 +14761,44 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>139</v>
+        <v>679</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>388</v>
+        <v>688</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>389</v>
+        <v>689</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>690</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>84</v>
       </c>
@@ -14790,19 +14846,19 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>390</v>
+        <v>687</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>84</v>
@@ -14820,7 +14876,7 @@
         <v>84</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>136</v>
+        <v>691</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
@@ -14831,10 +14887,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>677</v>
+        <v>692</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>677</v>
+        <v>692</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14857,13 +14913,13 @@
         <v>84</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>648</v>
+        <v>393</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>678</v>
+        <v>394</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>679</v>
+        <v>395</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14914,7 +14970,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>677</v>
+        <v>396</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -14926,7 +14982,7 @@
         <v>84</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>84</v>
@@ -14944,7 +15000,7 @@
         <v>84</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>680</v>
+        <v>397</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -14955,21 +15011,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>84</v>
@@ -14981,15 +15037,17 @@
         <v>84</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>682</v>
+        <v>139</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>683</v>
+        <v>140</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>84</v>
@@ -15038,19 +15096,19 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>681</v>
+        <v>402</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>84</v>
@@ -15068,7 +15126,7 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>685</v>
+        <v>397</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
@@ -15079,42 +15137,46 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>84</v>
+        <v>404</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>682</v>
+        <v>139</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>687</v>
+        <v>405</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
       </c>
@@ -15162,19 +15224,19 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>686</v>
+        <v>407</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>84</v>
@@ -15192,7 +15254,7 @@
         <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>685</v>
+        <v>136</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -15203,10 +15265,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15229,20 +15291,16 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>453</v>
+        <v>666</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>693</v>
-      </c>
+        <v>697</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>84</v>
       </c>
@@ -15290,7 +15348,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15317,10 +15375,10 @@
         <v>84</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>694</v>
+        <v>84</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15331,10 +15389,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15357,17 +15415,15 @@
         <v>84</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>554</v>
+        <v>700</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>699</v>
-      </c>
+        <v>702</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15416,7 +15472,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15443,24 +15499,24 @@
         <v>84</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>700</v>
+        <v>84</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>702</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15483,13 +15539,13 @@
         <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>648</v>
+        <v>700</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15540,7 +15596,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15567,24 +15623,24 @@
         <v>84</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>706</v>
+        <v>84</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR102" t="s" s="2">
-        <v>708</v>
+        <v>84</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15607,18 +15663,20 @@
         <v>84</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>682</v>
+        <v>471</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>710</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="N103" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>84</v>
       </c>
@@ -15666,7 +15724,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15693,10 +15751,10 @@
         <v>84</v>
       </c>
       <c r="AO103" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AP103" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
@@ -15707,10 +15765,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15733,15 +15791,17 @@
         <v>84</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>84</v>
@@ -15790,7 +15850,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15817,24 +15877,24 @@
         <v>84</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>84</v>
+        <v>718</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>719</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>308</v>
+        <v>84</v>
       </c>
       <c r="AR104" t="s" s="2">
-        <v>84</v>
+        <v>720</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15857,13 +15917,13 @@
         <v>84</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15914,7 +15974,7 @@
         <v>84</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15941,24 +16001,24 @@
         <v>84</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR105" t="s" s="2">
-        <v>84</v>
+        <v>726</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15981,15 +16041,17 @@
         <v>84</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>376</v>
+        <v>700</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>377</v>
+        <v>728</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>729</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>730</v>
+      </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>84</v>
@@ -16038,7 +16100,7 @@
         <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>379</v>
+        <v>727</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>82</v>
@@ -16050,7 +16112,7 @@
         <v>84</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>84</v>
@@ -16065,10 +16127,10 @@
         <v>84</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>84</v>
+        <v>731</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>380</v>
+        <v>732</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>84</v>
@@ -16079,21 +16141,21 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>84</v>
@@ -16105,17 +16167,15 @@
         <v>84</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>139</v>
+        <v>734</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>140</v>
+        <v>735</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>736</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>84</v>
@@ -16164,19 +16224,19 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>385</v>
+        <v>733</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>84</v>
@@ -16194,10 +16254,10 @@
         <v>84</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>380</v>
+        <v>737</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>84</v>
+        <v>325</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>84</v>
@@ -16205,46 +16265,42 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>727</v>
+        <v>738</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>727</v>
+        <v>738</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>139</v>
+        <v>679</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>388</v>
+        <v>739</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>740</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>84</v>
       </c>
@@ -16292,19 +16348,19 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>390</v>
+        <v>738</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>84</v>
@@ -16319,10 +16375,10 @@
         <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>84</v>
+        <v>741</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>136</v>
+        <v>742</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -16333,10 +16389,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>728</v>
+        <v>743</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>728</v>
+        <v>743</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16344,7 +16400,7 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>93</v>
@@ -16359,17 +16415,15 @@
         <v>84</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>568</v>
+        <v>393</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>729</v>
+        <v>394</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>731</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>84</v>
@@ -16394,13 +16448,13 @@
         <v>84</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>732</v>
+        <v>84</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>733</v>
+        <v>84</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>84</v>
@@ -16418,10 +16472,10 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>728</v>
+        <v>396</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>93</v>
@@ -16430,7 +16484,7 @@
         <v>84</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>84</v>
@@ -16445,35 +16499,35 @@
         <v>84</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>723</v>
+        <v>84</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>734</v>
+        <v>397</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>735</v>
+        <v>84</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>84</v>
@@ -16485,15 +16539,17 @@
         <v>84</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>737</v>
+        <v>140</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -16518,13 +16574,13 @@
         <v>84</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>739</v>
+        <v>84</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>740</v>
+        <v>84</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>84</v>
@@ -16542,19 +16598,19 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>736</v>
+        <v>402</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>84</v>
@@ -16569,56 +16625,60 @@
         <v>84</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>741</v>
+        <v>84</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>742</v>
+        <v>397</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>743</v>
+        <v>84</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>84</v>
+        <v>404</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I111" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I111" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="J111" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>745</v>
+        <v>139</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>746</v>
+        <v>405</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
       </c>
@@ -16666,37 +16726,37 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>744</v>
+        <v>407</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>748</v>
+        <v>84</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>749</v>
+        <v>84</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>750</v>
+        <v>84</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>741</v>
+        <v>84</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>751</v>
+        <v>136</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -16707,21 +16767,21 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>753</v>
+        <v>84</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>84</v>
@@ -16733,16 +16793,16 @@
         <v>84</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>754</v>
+        <v>586</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16768,13 +16828,13 @@
         <v>84</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>84</v>
+        <v>750</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>84</v>
+        <v>751</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>84</v>
@@ -16792,13 +16852,13 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>84</v>
@@ -16819,24 +16879,24 @@
         <v>84</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>84</v>
+        <v>741</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR112" t="s" s="2">
-        <v>84</v>
+        <v>753</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16847,7 +16907,7 @@
         <v>82</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>84</v>
@@ -16859,17 +16919,15 @@
         <v>84</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>760</v>
+        <v>175</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>763</v>
-      </c>
+        <v>756</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>84</v>
@@ -16894,13 +16952,13 @@
         <v>84</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>84</v>
+        <v>757</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>84</v>
+        <v>758</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>84</v>
@@ -16918,13 +16976,13 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>84</v>
@@ -16942,23 +17000,399 @@
         <v>84</v>
       </c>
       <c r="AN113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="AQ113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR113" t="s" s="2">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>764</v>
       </c>
-      <c r="AO113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP113" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>765</v>
       </c>
-      <c r="AQ113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR113" t="s" s="2">
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AQ114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR114" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="AQ115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR115" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="AQ116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR116" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR113">
+  <autoFilter ref="A1:AR116">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16968,7 +17402,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI112">
+  <conditionalFormatting sqref="A2:AI115">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4657" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4657" uniqueCount="785">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -500,7 +500,11 @@
     <t>This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
-    <t>1225: source value from ORDER - ORDER # (100-.01) case package like 'PS%' &amp; class 'I' &amp; [exclude supply]</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+mru-25-1225:If package like 'PS%' &amp; class 'I' &amp; [exclude supply] then source value from (100-.01) {null}</t>
+  </si>
+  <si>
+    <t>1225: source value based on ORDER - ORDER # (100-.01) if package like 'PS%' &amp; class 'I' &amp; [exclude supply]</t>
   </si>
   <si>
     <t>RadOrder.OrderItem[Order].Description,RadOrder.Extension[ResultExtension].null,LabOrder.OrderItem[Order].Description,LabOrder.Priority.Description,OtherOrder.OrderCategory.Description,OtherOrder.OrderItem[Order].Description,OtherOrder.OrderStatus[VA.VAStatus].Description,OtherOrder.Priority.Description,OtherOrder.OrderItem[Order].OriginalText</t>
@@ -809,7 +813,7 @@
     <t>medicationCodeableConcept</t>
   </si>
   <si>
-    <t>1549: source value from ORDER - ITEM ORDERED (100-7)</t>
+    <t>1549: source value based on ORDER - ITEM ORDERED (100-7)</t>
   </si>
   <si>
     <t>CPRSOrder.CPRSOrder.ItemOrderedParentFileIEN,CPRSOrder.CPRSOrder.ItemOrderedParentFileNumber</t>
@@ -844,7 +848,7 @@
     <t>The subject on a medication request is mandatory.  For the secondary use case where the actual subject is not provided, there still must be an anonymized subject specified.</t>
   </si>
   <si>
-    <t>1226: reference from ORDER - OBJECT OF ORDER (100-.02)</t>
+    <t>1226: reference based on ORDER - OBJECT OF ORDER (100-.02)</t>
   </si>
   <si>
     <t>CPRSOrder.OrderAction.ObjectOfOrderIEN,CPRSOrder.OrderAction.ObjectofOrderLabReferralPatientIEN,CPRSOrder.OrderAction.ObjectOfOrderPatientIEN,CPRSOrder.OrderAction.ParentFileNumber,CPRSOrder.OrderedItem.PatientIEN</t>
@@ -933,7 +937,7 @@
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
   </si>
   <si>
-    <t>1228: source value from ORDER - WHEN ENTERED (100-4)</t>
+    <t>1228: source value based on ORDER - WHEN ENTERED (100-4)</t>
   </si>
   <si>
     <t>CPRSOrder.CPRSOrder.EnteredDateTime,CPRSOrder.CPRSOrder.EnteredVistaDate,CPRSOrder.OrderedItem.EnteredDateTime,CPRSOrder.OrderedItem.EnteredVistaDate</t>
@@ -970,7 +974,7 @@
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
   </si>
   <si>
-    <t>1227: reference from ORDER - CURRENT AGENT/PROVIDER (100-1)</t>
+    <t>1227: reference based on ORDER - CURRENT AGENT/PROVIDER (100-1)</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -1532,7 +1536,7 @@
 </t>
   </si>
   <si>
-    <t>1234: source value from ORDER - START DATE (100-21)</t>
+    <t>1234: source value based on ORDER - START DATE (100-21)</t>
   </si>
   <si>
     <t>CPRSOrder.CPRSOrder.OrderStartDateTime,CPRSOrder.CPRSOrder.OrderStartVistaDate,CPRSOrder.OrderAction.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartDateSID,CPRSOrder.OrderedItem.OrderStartDateTime,CPRSOrder.OrderedItem.OrderStartVistaDate</t>
@@ -1568,7 +1572,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>1235: source value from ORDER - STOP DATE (100-22)</t>
+    <t>1235: source value based on ORDER - STOP DATE (100-22)</t>
   </si>
   <si>
     <t>CPRSOrder.CPRSOrder.OrderStopDateTime,CPRSOrder.CPRSOrder.OrderStopVistaDate,CPRSOrder.OrderedItem.OrderStopDateSID,CPRSOrder.OrderedItem.OrderStopDateTime,CPRSOrder.OrderedItem.OrderStopVistaDate</t>
@@ -2396,7 +2400,7 @@
     <t>A link to a resource representing an earlier order related order or prescription.</t>
   </si>
   <si>
-    <t>1232: reference from ORDER - REPLACED ORDER (100-9)</t>
+    <t>1232: reference based on ORDER - REPLACED ORDER (100-9)</t>
   </si>
   <si>
     <t>RadOrder.Extension[OrderExtension].ReplacedOrder,LabOrder.Extension[LabOrderExtension].ReplacedOrder,OtherOrder.Extension[OrderExtension].ReplacedOrder,Medication.Extension[MedicationExtension].ReplacedOrder</t>
@@ -2805,7 +2809,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="99.9140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="100.9453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="248.09765625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
@@ -4182,39 +4186,39 @@
         <v>84</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>155</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AR11" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -4240,13 +4244,13 @@
         <v>113</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -4272,13 +4276,13 @@
         <v>84</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>84</v>
@@ -4296,7 +4300,7 @@
         <v>84</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>93</v>
@@ -4311,7 +4315,7 @@
         <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>84</v>
@@ -4320,16 +4324,16 @@
         <v>84</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AR12" t="s" s="2">
         <v>84</v>
@@ -4337,10 +4341,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4363,16 +4367,16 @@
         <v>84</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4398,13 +4402,13 @@
         <v>84</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>84</v>
@@ -4422,7 +4426,7 @@
         <v>84</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>82</v>
@@ -4446,13 +4450,13 @@
         <v>84</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -4463,10 +4467,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4492,13 +4496,13 @@
         <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4524,13 +4528,13 @@
         <v>84</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>84</v>
@@ -4548,7 +4552,7 @@
         <v>84</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>93</v>
@@ -4563,7 +4567,7 @@
         <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>84</v>
@@ -4572,16 +4576,16 @@
         <v>84</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>84</v>
@@ -4589,10 +4593,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4615,16 +4619,16 @@
         <v>84</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4650,29 +4654,29 @@
         <v>84</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -4687,7 +4691,7 @@
         <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>84</v>
@@ -4699,13 +4703,13 @@
         <v>84</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -4713,13 +4717,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>84</v>
@@ -4741,16 +4745,16 @@
         <v>84</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4776,13 +4780,13 @@
         <v>84</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>84</v>
@@ -4800,7 +4804,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4815,7 +4819,7 @@
         <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>84</v>
@@ -4827,13 +4831,13 @@
         <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -4841,10 +4845,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4870,10 +4874,10 @@
         <v>113</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4900,13 +4904,13 @@
         <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>84</v>
@@ -4924,7 +4928,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4948,16 +4952,16 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>84</v>
@@ -4965,10 +4969,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4991,16 +4995,16 @@
         <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -5050,7 +5054,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -5080,7 +5084,7 @@
         <v>84</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -5091,10 +5095,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5117,13 +5121,13 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -5162,17 +5166,17 @@
         <v>84</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -5202,7 +5206,7 @@
         <v>84</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -5213,13 +5217,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>84</v>
@@ -5241,13 +5245,13 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -5298,7 +5302,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5313,7 +5317,7 @@
         <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>84</v>
@@ -5328,7 +5332,7 @@
         <v>84</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -5339,13 +5343,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>84</v>
@@ -5367,13 +5371,13 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5424,7 +5428,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5439,7 +5443,7 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>84</v>
@@ -5454,7 +5458,7 @@
         <v>84</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -5465,10 +5469,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5491,16 +5495,16 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5526,27 +5530,27 @@
         <v>84</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>93</v>
@@ -5570,30 +5574,30 @@
         <v>84</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>84</v>
@@ -5615,16 +5619,16 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5650,11 +5654,11 @@
         <v>84</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
@@ -5672,7 +5676,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>93</v>
@@ -5687,39 +5691,39 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5741,16 +5745,16 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5800,7 +5804,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>93</v>
@@ -5815,7 +5819,7 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>84</v>
@@ -5824,27 +5828,27 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5867,16 +5871,16 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5926,7 +5930,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>93</v>
@@ -5941,36 +5945,36 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5993,16 +5997,16 @@
         <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -6052,7 +6056,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -6067,7 +6071,7 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>84</v>
@@ -6076,27 +6080,27 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6119,13 +6123,13 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6176,7 +6180,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6200,16 +6204,16 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -6217,10 +6221,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6243,13 +6247,13 @@
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6300,7 +6304,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6315,36 +6319,36 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6367,13 +6371,13 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6424,7 +6428,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6439,7 +6443,7 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
@@ -6448,16 +6452,16 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -6465,10 +6469,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6491,13 +6495,13 @@
         <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6548,7 +6552,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6572,16 +6576,16 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -6589,10 +6593,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6615,16 +6619,16 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6650,13 +6654,13 @@
         <v>84</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>84</v>
@@ -6674,7 +6678,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6698,13 +6702,13 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6715,10 +6719,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6741,13 +6745,13 @@
         <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6798,7 +6802,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6828,10 +6832,10 @@
         <v>84</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6839,10 +6843,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6865,16 +6869,16 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6900,13 +6904,13 @@
         <v>84</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
@@ -6924,7 +6928,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6948,27 +6952,27 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6991,16 +6995,16 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -7050,7 +7054,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -7074,16 +7078,16 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -7091,10 +7095,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7117,13 +7121,13 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7174,7 +7178,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7198,13 +7202,13 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -7215,10 +7219,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7244,10 +7248,10 @@
         <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7298,7 +7302,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7328,7 +7332,7 @@
         <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -7339,10 +7343,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7365,13 +7369,13 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7422,7 +7426,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7446,13 +7450,13 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -7463,10 +7467,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7492,14 +7496,14 @@
         <v>151</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -7548,7 +7552,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7572,13 +7576,13 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7589,10 +7593,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7615,16 +7619,16 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7650,13 +7654,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7674,7 +7678,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7704,7 +7708,7 @@
         <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7715,10 +7719,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7741,13 +7745,13 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7798,7 +7802,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7822,13 +7826,13 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7839,10 +7843,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7865,13 +7869,13 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7922,7 +7926,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7946,13 +7950,13 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7963,10 +7967,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7989,16 +7993,16 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -8048,7 +8052,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -8072,13 +8076,13 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -8089,10 +8093,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8115,13 +8119,13 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8172,7 +8176,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8202,7 +8206,7 @@
         <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -8213,10 +8217,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8245,7 +8249,7 @@
         <v>140</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>142</v>
@@ -8286,19 +8290,19 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8328,7 +8332,7 @@
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8339,14 +8343,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -8368,10 +8372,10 @@
         <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>142</v>
@@ -8426,7 +8430,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8467,10 +8471,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8493,17 +8497,17 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8552,7 +8556,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8582,21 +8586,21 @@
         <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8619,17 +8623,17 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8678,7 +8682,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8693,7 +8697,7 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>84</v>
@@ -8708,21 +8712,21 @@
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8745,19 +8749,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8782,13 +8786,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8806,7 +8810,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8836,21 +8840,21 @@
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8873,13 +8877,13 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8930,7 +8934,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8960,21 +8964,21 @@
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8997,19 +9001,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -9058,7 +9062,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9088,7 +9092,7 @@
         <v>84</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -9099,10 +9103,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9125,13 +9129,13 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9182,7 +9186,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9212,7 +9216,7 @@
         <v>84</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -9223,10 +9227,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9255,7 +9259,7 @@
         <v>140</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>142</v>
@@ -9296,19 +9300,19 @@
         <v>84</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9338,7 +9342,7 @@
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -9349,14 +9353,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -9378,10 +9382,10 @@
         <v>139</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>142</v>
@@ -9436,7 +9440,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9477,10 +9481,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9503,17 +9507,17 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9562,7 +9566,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9592,7 +9596,7 @@
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9603,10 +9607,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9629,17 +9633,17 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9688,7 +9692,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9700,7 +9704,7 @@
         <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>84</v>
@@ -9718,7 +9722,7 @@
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9729,10 +9733,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9755,13 +9759,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9812,7 +9816,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9842,7 +9846,7 @@
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9853,10 +9857,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9885,7 +9889,7 @@
         <v>140</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>142</v>
@@ -9926,19 +9930,19 @@
         <v>84</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9968,7 +9972,7 @@
         <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9979,10 +9983,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10005,13 +10009,13 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -10050,17 +10054,17 @@
         <v>84</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10090,7 +10094,7 @@
         <v>84</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -10101,13 +10105,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>84</v>
@@ -10129,13 +10133,13 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10186,7 +10190,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10216,7 +10220,7 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -10227,10 +10231,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10253,13 +10257,13 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10310,7 +10314,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10340,7 +10344,7 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10351,10 +10355,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10383,7 +10387,7 @@
         <v>140</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>142</v>
@@ -10424,19 +10428,19 @@
         <v>84</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10466,7 +10470,7 @@
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10477,10 +10481,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10503,16 +10507,16 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10562,7 +10566,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10571,19 +10575,19 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>84</v>
@@ -10592,21 +10596,21 @@
         <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10629,23 +10633,23 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>84</v>
@@ -10690,7 +10694,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10699,19 +10703,19 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>84</v>
@@ -10720,21 +10724,21 @@
         <v>84</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10757,19 +10761,19 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10818,7 +10822,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10848,7 +10852,7 @@
         <v>84</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10859,10 +10863,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10885,13 +10889,13 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10942,7 +10946,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10972,7 +10976,7 @@
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10983,10 +10987,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11009,19 +11013,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -11070,7 +11074,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11100,7 +11104,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11111,10 +11115,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11137,19 +11141,19 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -11198,7 +11202,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11228,7 +11232,7 @@
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -11239,10 +11243,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11268,10 +11272,10 @@
         <v>113</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -11298,13 +11302,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -11322,7 +11326,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11352,7 +11356,7 @@
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11363,10 +11367,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11389,13 +11393,13 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11403,7 +11407,7 @@
         <v>84</v>
       </c>
       <c r="Q69" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="R69" t="s" s="2">
         <v>84</v>
@@ -11448,7 +11452,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11478,7 +11482,7 @@
         <v>84</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11489,10 +11493,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11515,13 +11519,13 @@
         <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11572,7 +11576,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11602,7 +11606,7 @@
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11613,10 +11617,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11639,13 +11643,13 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11696,7 +11700,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11726,7 +11730,7 @@
         <v>84</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11737,10 +11741,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11763,13 +11767,13 @@
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11820,7 +11824,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11850,7 +11854,7 @@
         <v>84</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11861,10 +11865,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11890,10 +11894,10 @@
         <v>113</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11920,13 +11924,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -11944,7 +11948,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11974,7 +11978,7 @@
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11985,10 +11989,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12014,13 +12018,13 @@
         <v>113</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12046,11 +12050,11 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -12068,7 +12072,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12098,7 +12102,7 @@
         <v>84</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12109,10 +12113,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12135,16 +12139,16 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12194,7 +12198,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12224,7 +12228,7 @@
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -12235,10 +12239,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12264,16 +12268,16 @@
         <v>113</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -12298,13 +12302,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12322,7 +12326,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12352,7 +12356,7 @@
         <v>84</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12363,10 +12367,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12389,13 +12393,13 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12446,7 +12450,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12476,7 +12480,7 @@
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12487,10 +12491,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12513,16 +12517,16 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12551,10 +12555,10 @@
         <v>117</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12572,7 +12576,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12602,7 +12606,7 @@
         <v>84</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12613,10 +12617,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12639,16 +12643,16 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12674,13 +12678,13 @@
         <v>84</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12698,7 +12702,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12728,21 +12732,21 @@
         <v>84</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12765,19 +12769,19 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12802,13 +12806,13 @@
         <v>84</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>84</v>
@@ -12826,7 +12830,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12856,21 +12860,21 @@
         <v>84</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12893,17 +12897,17 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>84</v>
@@ -12928,13 +12932,13 @@
         <v>84</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -12952,7 +12956,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12982,21 +12986,21 @@
         <v>84</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR81" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13019,19 +13023,19 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -13056,13 +13060,13 @@
         <v>84</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>84</v>
@@ -13080,7 +13084,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13110,21 +13114,21 @@
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13147,13 +13151,13 @@
         <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -13204,7 +13208,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13240,15 +13244,15 @@
         <v>84</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13271,13 +13275,13 @@
         <v>84</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -13328,7 +13332,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13358,7 +13362,7 @@
         <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13369,10 +13373,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13401,7 +13405,7 @@
         <v>140</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>142</v>
@@ -13442,19 +13446,19 @@
         <v>84</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13484,7 +13488,7 @@
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13495,10 +13499,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13521,17 +13525,17 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>84</v>
@@ -13556,13 +13560,13 @@
         <v>84</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>84</v>
@@ -13580,7 +13584,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13616,15 +13620,15 @@
         <v>84</v>
       </c>
       <c r="AR86" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13647,19 +13651,19 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
@@ -13708,7 +13712,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13738,21 +13742,21 @@
         <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13775,19 +13779,19 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13836,7 +13840,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13866,21 +13870,21 @@
         <v>84</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13903,19 +13907,19 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -13964,7 +13968,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13994,21 +13998,21 @@
         <v>84</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14031,19 +14035,19 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -14092,7 +14096,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14122,7 +14126,7 @@
         <v>84</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14133,10 +14137,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14159,17 +14163,17 @@
         <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -14218,7 +14222,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14248,7 +14252,7 @@
         <v>84</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14259,10 +14263,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14285,13 +14289,13 @@
         <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -14342,7 +14346,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14369,10 +14373,10 @@
         <v>84</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14383,10 +14387,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14409,13 +14413,13 @@
         <v>84</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -14466,7 +14470,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14496,7 +14500,7 @@
         <v>84</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14507,10 +14511,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14539,7 +14543,7 @@
         <v>140</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>142</v>
@@ -14592,7 +14596,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14622,7 +14626,7 @@
         <v>84</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
@@ -14633,14 +14637,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -14662,10 +14666,10 @@
         <v>139</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>142</v>
@@ -14720,7 +14724,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14761,10 +14765,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14787,16 +14791,16 @@
         <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14846,7 +14850,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14876,7 +14880,7 @@
         <v>84</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
@@ -14887,10 +14891,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14913,13 +14917,13 @@
         <v>84</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14970,7 +14974,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15000,7 +15004,7 @@
         <v>84</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -15011,10 +15015,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15043,7 +15047,7 @@
         <v>140</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>142</v>
@@ -15096,7 +15100,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15126,7 +15130,7 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
@@ -15137,14 +15141,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15166,10 +15170,10 @@
         <v>139</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>142</v>
@@ -15224,7 +15228,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15265,10 +15269,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15291,13 +15295,13 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15348,7 +15352,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15378,7 +15382,7 @@
         <v>84</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15389,10 +15393,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15415,13 +15419,13 @@
         <v>84</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15472,7 +15476,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15502,7 +15506,7 @@
         <v>84</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
@@ -15513,10 +15517,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15539,13 +15543,13 @@
         <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15596,7 +15600,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15626,7 +15630,7 @@
         <v>84</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
@@ -15637,10 +15641,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15663,19 +15667,19 @@
         <v>84</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -15724,7 +15728,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15751,10 +15755,10 @@
         <v>84</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
@@ -15765,10 +15769,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15791,16 +15795,16 @@
         <v>84</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15850,7 +15854,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15877,24 +15881,24 @@
         <v>84</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR104" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15917,13 +15921,13 @@
         <v>84</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15974,7 +15978,7 @@
         <v>84</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -16001,24 +16005,24 @@
         <v>84</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR105" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16041,16 +16045,16 @@
         <v>84</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -16100,7 +16104,7 @@
         <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>82</v>
@@ -16127,10 +16131,10 @@
         <v>84</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>84</v>
@@ -16141,10 +16145,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16167,13 +16171,13 @@
         <v>84</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -16224,7 +16228,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16254,10 +16258,10 @@
         <v>84</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>84</v>
@@ -16265,10 +16269,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16291,13 +16295,13 @@
         <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -16348,7 +16352,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16375,10 +16379,10 @@
         <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -16389,10 +16393,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16415,13 +16419,13 @@
         <v>84</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -16472,7 +16476,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16502,7 +16506,7 @@
         <v>84</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
@@ -16513,10 +16517,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16545,7 +16549,7 @@
         <v>140</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>142</v>
@@ -16598,7 +16602,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -16628,7 +16632,7 @@
         <v>84</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
@@ -16639,14 +16643,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -16668,10 +16672,10 @@
         <v>139</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>142</v>
@@ -16726,7 +16730,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16767,10 +16771,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16793,16 +16797,16 @@
         <v>84</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16828,13 +16832,13 @@
         <v>84</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>84</v>
@@ -16852,7 +16856,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>93</v>
@@ -16879,24 +16883,24 @@
         <v>84</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR112" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16919,13 +16923,13 @@
         <v>84</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16952,13 +16956,13 @@
         <v>84</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>84</v>
@@ -16976,7 +16980,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17003,24 +17007,24 @@
         <v>84</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR113" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17043,13 +17047,13 @@
         <v>84</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -17100,7 +17104,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17115,22 +17119,22 @@
         <v>105</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
@@ -17141,14 +17145,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -17167,16 +17171,16 @@
         <v>84</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -17226,7 +17230,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17256,7 +17260,7 @@
         <v>84</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
@@ -17267,10 +17271,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17293,16 +17297,16 @@
         <v>84</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -17352,7 +17356,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17376,13 +17380,13 @@
         <v>84</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4978" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4978" uniqueCount="835">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -615,7 +615,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mru-25-1225-1:If (undefined) is package like 'PS%' &amp; class 'I' &amp; [exclude supply] then fixed value http://terminology.hl7.org/CodeSystem/v2-0203/identifier-type#PLAC {null}</t>
+mru-25-1225-1:If package like 'PS%' &amp; class 'I' &amp; [exclude supply] then fixed value http://terminology.hl7.org/CodeSystem/v2-0203/identifier-type#PLAC {true}</t>
   </si>
   <si>
     <t>1225-1: fixed value = http://terminology.hl7.org/CodeSystem/v2-0203/identifier-type#PLAC if package like 'PS%' &amp; class 'I' &amp; [exclude supply]</t>
@@ -670,7 +670,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mru-25-1225:If package like 'PS%' &amp; class 'I' &amp; [exclude supply] then source value from (100-.01) {null}</t>
+mru-25-1225:If package like 'PS%' &amp; class 'I' &amp; [exclude supply] then source value from (100-.01) {true}</t>
   </si>
   <si>
     <t>1225: source value based on ORDER - ORDER # (100-.01) if package like 'PS%' &amp; class 'I' &amp; [exclude supply]</t>
@@ -848,9 +848,6 @@
 </t>
   </si>
   <si>
-    <t>2170: target not supported</t>
-  </si>
-  <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions  or @@ -868,9 +865,6 @@
   </si>
   <si>
     <t>The type of medication order.</t>
-  </si>
-  <si>
-    <t>2171: target not supported</t>
   </si>
   <si>
     <t>MedicationRequest.priority</t>
@@ -5858,22 +5852,22 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>259</v>
@@ -5884,13 +5878,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>260</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5950,7 +5944,7 @@
         <v>177</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>265</v>
@@ -5986,7 +5980,7 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>273</v>
+        <v>84</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>84</v>
@@ -5998,10 +5992,10 @@
         <v>84</v>
       </c>
       <c r="AO24" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>259</v>
@@ -6012,10 +6006,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -6041,10 +6035,10 @@
         <v>113</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -6074,10 +6068,10 @@
         <v>177</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -6095,7 +6089,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -6119,16 +6113,16 @@
         <v>84</v>
       </c>
       <c r="AN25" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>84</v>
@@ -6136,10 +6130,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6162,16 +6156,16 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -6221,7 +6215,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -6251,7 +6245,7 @@
         <v>84</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -6262,10 +6256,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6288,13 +6282,13 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6333,17 +6327,17 @@
         <v>84</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6373,7 +6367,7 @@
         <v>84</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -6384,13 +6378,13 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>84</v>
@@ -6412,13 +6406,13 @@
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6469,7 +6463,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6484,7 +6478,7 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -6499,7 +6493,7 @@
         <v>84</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -6510,13 +6504,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>84</v>
@@ -6538,13 +6532,13 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6595,7 +6589,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6610,7 +6604,7 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
@@ -6625,7 +6619,7 @@
         <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -6636,10 +6630,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6662,16 +6656,16 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6701,23 +6695,23 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>93</v>
@@ -6741,30 +6735,30 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AP30" t="s" s="2">
+      <c r="AR30" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>84</v>
@@ -6789,13 +6783,13 @@
         <v>183</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6825,7 +6819,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>84</v>
@@ -6843,7 +6837,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>93</v>
@@ -6858,39 +6852,39 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AO31" t="s" s="2">
+      <c r="AQ31" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AP31" t="s" s="2">
+      <c r="AR31" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AR31" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>84</v>
@@ -6912,16 +6906,16 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6971,7 +6965,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>93</v>
@@ -6986,7 +6980,7 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
@@ -6995,27 +6989,27 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AQ32" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AP32" t="s" s="2">
+      <c r="AR32" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AR32" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7038,16 +7032,16 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -7097,7 +7091,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>93</v>
@@ -7112,36 +7106,36 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AQ33" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AP33" t="s" s="2">
+      <c r="AR33" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AR33" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7164,16 +7158,16 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -7223,7 +7217,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -7238,7 +7232,7 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
@@ -7247,27 +7241,27 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>238</v>
       </c>
       <c r="AP34" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AR34" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AR34" t="s" s="2">
-        <v>343</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7290,13 +7284,13 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7347,7 +7341,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7371,16 +7365,16 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -7388,10 +7382,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7414,13 +7408,13 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7471,7 +7465,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7486,36 +7480,36 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AQ36" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AP36" t="s" s="2">
+      <c r="AR36" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AR36" t="s" s="2">
-        <v>361</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7538,13 +7532,13 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7595,7 +7589,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7610,25 +7604,25 @@
         <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -7636,10 +7630,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7662,13 +7656,13 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7719,7 +7713,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7743,16 +7737,16 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7760,10 +7754,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7789,13 +7783,13 @@
         <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7824,10 +7818,10 @@
         <v>245</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7845,7 +7839,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7869,13 +7863,13 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7886,10 +7880,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7912,13 +7906,13 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7969,7 +7963,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7999,10 +7993,10 @@
         <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -8010,10 +8004,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8039,13 +8033,13 @@
         <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8074,10 +8068,10 @@
         <v>245</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -8095,7 +8089,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -8119,27 +8113,27 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AP41" t="s" s="2">
+      <c r="AR41" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>400</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8162,16 +8156,16 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -8221,7 +8215,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -8245,16 +8239,16 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>238</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -8262,10 +8256,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8288,13 +8282,13 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8345,7 +8339,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8369,13 +8363,13 @@
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -8386,10 +8380,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8415,10 +8409,10 @@
         <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -8469,7 +8463,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8499,7 +8493,7 @@
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8510,10 +8504,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8536,13 +8530,13 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8593,7 +8587,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8617,13 +8611,13 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8634,10 +8628,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8663,14 +8657,14 @@
         <v>151</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8719,7 +8713,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8743,13 +8737,13 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8760,10 +8754,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8789,13 +8783,13 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8824,10 +8818,10 @@
         <v>245</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8845,7 +8839,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8875,7 +8869,7 @@
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8886,10 +8880,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8912,13 +8906,13 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8969,7 +8963,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8993,13 +8987,13 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -9010,10 +9004,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9036,13 +9030,13 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -9093,7 +9087,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -9117,13 +9111,13 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -9134,10 +9128,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9160,16 +9154,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -9219,7 +9213,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9243,13 +9237,13 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -9260,10 +9254,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9384,10 +9378,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9510,14 +9504,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -9539,10 +9533,10 @@
         <v>139</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>142</v>
@@ -9597,7 +9591,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9638,10 +9632,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9664,17 +9658,17 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9723,7 +9717,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9753,21 +9747,21 @@
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9793,14 +9787,14 @@
         <v>161</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9849,7 +9843,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9864,7 +9858,7 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>84</v>
@@ -9879,21 +9873,21 @@
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9919,16 +9913,16 @@
         <v>183</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9956,28 +9950,28 @@
         <v>245</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -10007,21 +10001,21 @@
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10047,10 +10041,10 @@
         <v>161</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -10101,7 +10095,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -10131,21 +10125,21 @@
         <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10168,19 +10162,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -10229,7 +10223,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10259,7 +10253,7 @@
         <v>84</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -10270,10 +10264,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10394,10 +10388,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10520,14 +10514,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -10549,10 +10543,10 @@
         <v>139</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>142</v>
@@ -10607,7 +10601,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10648,10 +10642,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10674,17 +10668,17 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10733,7 +10727,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10763,7 +10757,7 @@
         <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10774,10 +10768,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10800,17 +10794,17 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10859,7 +10853,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10871,7 +10865,7 @@
         <v>84</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>84</v>
@@ -10889,7 +10883,7 @@
         <v>84</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10900,10 +10894,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11024,10 +11018,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11150,10 +11144,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11176,13 +11170,13 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -11221,7 +11215,7 @@
         <v>84</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
@@ -11231,7 +11225,7 @@
         <v>170</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11261,7 +11255,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11272,13 +11266,13 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>84</v>
@@ -11303,10 +11297,10 @@
         <v>216</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11357,7 +11351,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11387,7 +11381,7 @@
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -11398,10 +11392,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11522,10 +11516,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11648,10 +11642,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11674,16 +11668,16 @@
         <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11733,7 +11727,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11742,42 +11736,42 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AL70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>541</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11800,23 +11794,23 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q71" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="R71" t="s" s="2">
         <v>84</v>
@@ -11861,7 +11855,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11870,42 +11864,42 @@
         <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AQ71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR71" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>553</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11928,19 +11922,19 @@
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11989,7 +11983,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -12019,7 +12013,7 @@
         <v>84</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -12030,10 +12024,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12056,13 +12050,13 @@
         <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -12113,7 +12107,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -12143,7 +12137,7 @@
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -12154,10 +12148,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12180,19 +12174,19 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -12241,7 +12235,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12271,7 +12265,7 @@
         <v>84</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12282,10 +12276,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12308,19 +12302,19 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -12369,7 +12363,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12399,7 +12393,7 @@
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -12410,10 +12404,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12439,10 +12433,10 @@
         <v>113</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12472,28 +12466,28 @@
         <v>177</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12523,7 +12517,7 @@
         <v>84</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12534,10 +12528,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12560,13 +12554,13 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12574,7 +12568,7 @@
         <v>84</v>
       </c>
       <c r="Q77" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="R77" t="s" s="2">
         <v>84</v>
@@ -12619,7 +12613,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12649,7 +12643,7 @@
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12660,10 +12654,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12686,13 +12680,13 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12743,7 +12737,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12773,7 +12767,7 @@
         <v>84</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12784,10 +12778,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12810,13 +12804,13 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12867,7 +12861,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12897,7 +12891,7 @@
         <v>84</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12908,10 +12902,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12934,13 +12928,13 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12991,7 +12985,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -13021,7 +13015,7 @@
         <v>84</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
@@ -13032,10 +13026,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13061,10 +13055,10 @@
         <v>113</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -13094,10 +13088,10 @@
         <v>177</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -13115,7 +13109,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13145,7 +13139,7 @@
         <v>84</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -13156,10 +13150,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13185,13 +13179,13 @@
         <v>113</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13221,7 +13215,7 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>84</v>
@@ -13239,7 +13233,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13280,10 +13274,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13306,16 +13300,16 @@
         <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13365,7 +13359,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13406,10 +13400,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13435,16 +13429,16 @@
         <v>113</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13472,28 +13466,28 @@
         <v>177</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13523,7 +13517,7 @@
         <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13534,10 +13528,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13560,13 +13554,13 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13617,7 +13611,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13647,7 +13641,7 @@
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13658,10 +13652,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13687,13 +13681,13 @@
         <v>183</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -13722,28 +13716,28 @@
         <v>117</v>
       </c>
       <c r="Y86" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13773,7 +13767,7 @@
         <v>84</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13784,10 +13778,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13810,16 +13804,16 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13848,28 +13842,28 @@
         <v>245</v>
       </c>
       <c r="Y87" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13899,21 +13893,21 @@
         <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13939,16 +13933,16 @@
         <v>183</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13976,28 +13970,28 @@
         <v>245</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -14027,21 +14021,21 @@
         <v>84</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14067,14 +14061,14 @@
         <v>183</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -14102,28 +14096,28 @@
         <v>245</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14153,21 +14147,21 @@
         <v>84</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14193,16 +14187,16 @@
         <v>183</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -14230,28 +14224,28 @@
         <v>245</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14281,21 +14275,21 @@
         <v>84</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14318,13 +14312,13 @@
         <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -14375,7 +14369,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14411,15 +14405,15 @@
         <v>84</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14540,10 +14534,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14666,10 +14660,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14695,14 +14689,14 @@
         <v>183</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14730,28 +14724,28 @@
         <v>245</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14787,15 +14781,15 @@
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14818,19 +14812,19 @@
         <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>698</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14879,7 +14873,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14909,21 +14903,21 @@
         <v>84</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14946,19 +14940,19 @@
         <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -15007,7 +15001,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -15037,21 +15031,21 @@
         <v>84</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15074,19 +15068,19 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15135,7 +15129,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15165,21 +15159,21 @@
         <v>84</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15202,19 +15196,19 @@
         <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>724</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>84</v>
@@ -15263,7 +15257,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15293,7 +15287,7 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
@@ -15304,10 +15298,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15330,17 +15324,17 @@
         <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
@@ -15389,7 +15383,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15419,7 +15413,7 @@
         <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -15430,10 +15424,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15456,13 +15450,13 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>735</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15513,7 +15507,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15540,10 +15534,10 @@
         <v>84</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15554,10 +15548,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15678,10 +15672,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15804,14 +15798,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -15833,10 +15827,10 @@
         <v>139</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>142</v>
@@ -15891,7 +15885,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15932,10 +15926,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15958,16 +15952,16 @@
         <v>84</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -16017,7 +16011,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -16047,7 +16041,7 @@
         <v>84</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
@@ -16058,10 +16052,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16182,10 +16176,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16308,14 +16302,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -16337,10 +16331,10 @@
         <v>139</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>142</v>
@@ -16395,7 +16389,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16436,10 +16430,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16462,13 +16456,13 @@
         <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -16519,7 +16513,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16549,7 +16543,7 @@
         <v>84</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -16560,10 +16554,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16586,13 +16580,13 @@
         <v>84</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>754</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>756</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -16643,7 +16637,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16673,7 +16667,7 @@
         <v>84</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
@@ -16684,10 +16678,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16710,13 +16704,13 @@
         <v>84</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -16767,7 +16761,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -16797,7 +16791,7 @@
         <v>84</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
@@ -16808,10 +16802,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16837,16 +16831,16 @@
         <v>216</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>762</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -16895,7 +16889,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16922,10 +16916,10 @@
         <v>84</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -16936,10 +16930,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16962,16 +16956,16 @@
         <v>84</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>771</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -17021,7 +17015,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -17048,24 +17042,24 @@
         <v>84</v>
       </c>
       <c r="AO112" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="AQ112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR112" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="AQ112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR112" t="s" s="2">
-        <v>774</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17088,13 +17082,13 @@
         <v>84</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -17145,7 +17139,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17172,24 +17166,24 @@
         <v>84</v>
       </c>
       <c r="AO113" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="AQ113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR113" t="s" s="2">
         <v>778</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="AQ113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR113" t="s" s="2">
-        <v>780</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17212,16 +17206,16 @@
         <v>84</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="N114" t="s" s="2">
         <v>782</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -17271,7 +17265,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17298,10 +17292,10 @@
         <v>84</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
@@ -17312,10 +17306,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17341,10 +17335,10 @@
         <v>223</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -17395,7 +17389,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17425,10 +17419,10 @@
         <v>84</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="AQ115" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>84</v>
@@ -17436,10 +17430,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17462,13 +17456,13 @@
         <v>84</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -17519,7 +17513,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17546,10 +17540,10 @@
         <v>84</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
@@ -17560,10 +17554,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17684,10 +17678,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17810,14 +17804,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -17839,10 +17833,10 @@
         <v>139</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>142</v>
@@ -17897,7 +17891,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -17938,10 +17932,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17964,16 +17958,16 @@
         <v>84</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="N120" t="s" s="2">
         <v>800</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>802</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -18002,10 +17996,10 @@
         <v>245</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>84</v>
@@ -18023,7 +18017,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>93</v>
@@ -18050,24 +18044,24 @@
         <v>84</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="AQ120" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR120" t="s" s="2">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18093,10 +18087,10 @@
         <v>183</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -18126,10 +18120,10 @@
         <v>245</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>84</v>
@@ -18147,7 +18141,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18174,24 +18168,24 @@
         <v>84</v>
       </c>
       <c r="AO121" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="AQ121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR121" t="s" s="2">
         <v>812</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="AQ121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR121" t="s" s="2">
-        <v>814</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18214,13 +18208,13 @@
         <v>84</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>816</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18271,7 +18265,7 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18286,22 +18280,22 @@
         <v>105</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>819</v>
       </c>
-      <c r="AL122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM122" t="s" s="2">
+      <c r="AO122" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="AP122" t="s" s="2">
         <v>820</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18312,14 +18306,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -18338,16 +18332,16 @@
         <v>84</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>825</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>828</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -18397,7 +18391,7 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>82</v>
@@ -18427,7 +18421,7 @@
         <v>84</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>84</v>
@@ -18438,10 +18432,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18464,16 +18458,16 @@
         <v>84</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>831</v>
       </c>
-      <c r="L124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>832</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>834</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -18523,7 +18517,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18547,13 +18541,13 @@
         <v>84</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -615,10 +615,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mru-25-1225-1:If package like 'PS%' &amp; class 'I' &amp; [exclude supply] then fixed value http://terminology.hl7.org/CodeSystem/v2-0203/identifier-type#PLAC {true}</t>
-  </si>
-  <si>
-    <t>1225-1: fixed value = http://terminology.hl7.org/CodeSystem/v2-0203/identifier-type#PLAC if package like 'PS%' &amp; class 'I' &amp; [exclude supply]</t>
+mru-25-1225-1:If package like 'PS%' &amp; class 'I' &amp; [exclude supply] then fixed value http://terminology.hl7.org/CodeSystem/v2-0203#PLAC {true}</t>
+  </si>
+  <si>
+    <t>1225-1: fixed value = http://terminology.hl7.org/CodeSystem/v2-0203#PLAC if package like 'PS%' &amp; class 'I' &amp; [exclude supply]</t>
   </si>
   <si>
     <t>CX.5</t>
@@ -2960,7 +2960,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="132.015625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="118.4140625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="248.09765625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsigned.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
